--- a/research/traditional_assets/database/data/bulgaria/bulgaria_transportation.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_transportation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09879720847127524</v>
+        <v>0.09873891126280396</v>
       </c>
       <c r="C2">
-        <v>649.9743409939085</v>
+        <v>644.2370479565008</v>
       </c>
       <c r="D2">
-        <v>629.4743409939085</v>
+        <v>630.1010479565008</v>
       </c>
       <c r="E2">
-        <v>-54.2</v>
+        <v>-47.836</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.364000000000001</v>
       </c>
       <c r="G2">
         <v>20.5</v>
@@ -1451,28 +1451,28 @@
         <v>27.3</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3201092</v>
       </c>
       <c r="N2">
-        <v>27.3</v>
+        <v>26.9798908</v>
       </c>
       <c r="O2">
-        <v>2.73</v>
+        <v>2.69798908</v>
       </c>
       <c r="P2">
-        <v>24.57</v>
+        <v>24.28190172</v>
       </c>
       <c r="Q2">
-        <v>47.27</v>
+        <v>46.98190172</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09879720847127524</v>
+        <v>0.09927900127555955</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8273031413723911</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>85.28339704075982</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09873891126280396</v>
+        <v>0.09868061405433269</v>
       </c>
       <c r="C3">
-        <v>644.2370479565008</v>
+        <v>638.5010040662493</v>
       </c>
       <c r="D3">
-        <v>630.1010479565008</v>
+        <v>630.7290040662492</v>
       </c>
       <c r="E3">
-        <v>-47.836</v>
+        <v>-41.472</v>
       </c>
       <c r="F3">
-        <v>6.364000000000001</v>
+        <v>12.728</v>
       </c>
       <c r="G3">
         <v>20.5</v>
@@ -1533,28 +1533,28 @@
         <v>27.3</v>
       </c>
       <c r="M3">
-        <v>0.3201092</v>
+        <v>0.6402184000000001</v>
       </c>
       <c r="N3">
-        <v>26.9798908</v>
+        <v>26.6597816</v>
       </c>
       <c r="O3">
-        <v>2.69798908</v>
+        <v>2.66597816</v>
       </c>
       <c r="P3">
-        <v>24.28190172</v>
+        <v>23.99380344</v>
       </c>
       <c r="Q3">
-        <v>46.98190172</v>
+        <v>46.69380344</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09927900127555955</v>
+        <v>0.09977062658605376</v>
       </c>
       <c r="T3">
-        <v>0.8273031413723911</v>
+        <v>0.8349084285701518</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>85.28339704075982</v>
+        <v>42.64169852037992</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09868061405433269</v>
+        <v>0.0986223168458614</v>
       </c>
       <c r="C4">
-        <v>638.5010040662493</v>
+        <v>632.7662130615651</v>
       </c>
       <c r="D4">
-        <v>630.7290040662492</v>
+        <v>631.358213061565</v>
       </c>
       <c r="E4">
-        <v>-41.472</v>
+        <v>-35.108</v>
       </c>
       <c r="F4">
-        <v>12.728</v>
+        <v>19.092</v>
       </c>
       <c r="G4">
         <v>20.5</v>
@@ -1615,28 +1615,28 @@
         <v>27.3</v>
       </c>
       <c r="M4">
-        <v>0.6402184000000001</v>
+        <v>0.9603276000000001</v>
       </c>
       <c r="N4">
-        <v>26.6597816</v>
+        <v>26.3396724</v>
       </c>
       <c r="O4">
-        <v>2.66597816</v>
+        <v>2.63396724</v>
       </c>
       <c r="P4">
-        <v>23.99380344</v>
+        <v>23.70570516</v>
       </c>
       <c r="Q4">
-        <v>46.69380344</v>
+        <v>46.40570516</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09977062658605376</v>
+        <v>0.100272388500888</v>
       </c>
       <c r="T4">
-        <v>0.8349084285701518</v>
+        <v>0.8426705258132269</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.64169852037992</v>
+        <v>28.42779901358661</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0986223168458614</v>
+        <v>0.09856401963739013</v>
       </c>
       <c r="C5">
-        <v>632.7662130615651</v>
+        <v>627.0326786957903</v>
       </c>
       <c r="D5">
-        <v>631.358213061565</v>
+        <v>631.9886786957903</v>
       </c>
       <c r="E5">
-        <v>-35.108</v>
+        <v>-28.744</v>
       </c>
       <c r="F5">
-        <v>19.092</v>
+        <v>25.456</v>
       </c>
       <c r="G5">
         <v>20.5</v>
@@ -1697,28 +1697,28 @@
         <v>27.3</v>
       </c>
       <c r="M5">
-        <v>0.9603276000000001</v>
+        <v>1.2804368</v>
       </c>
       <c r="N5">
-        <v>26.3396724</v>
+        <v>26.0195632</v>
       </c>
       <c r="O5">
-        <v>2.63396724</v>
+        <v>2.60195632</v>
       </c>
       <c r="P5">
-        <v>23.70570516</v>
+        <v>23.41760688</v>
       </c>
       <c r="Q5">
-        <v>46.40570516</v>
+        <v>46.11760688</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.100272388500888</v>
+        <v>0.1007846037889481</v>
       </c>
       <c r="T5">
-        <v>0.8426705258132269</v>
+        <v>0.8505943334155329</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.42779901358661</v>
+        <v>21.32084926018996</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09856401963739013</v>
+        <v>0.09850572242891885</v>
       </c>
       <c r="C6">
-        <v>627.0326786957903</v>
+        <v>621.3004047372756</v>
       </c>
       <c r="D6">
-        <v>631.9886786957903</v>
+        <v>632.6204047372756</v>
       </c>
       <c r="E6">
-        <v>-28.744</v>
+        <v>-22.38</v>
       </c>
       <c r="F6">
-        <v>25.456</v>
+        <v>31.82000000000001</v>
       </c>
       <c r="G6">
         <v>20.5</v>
@@ -1779,28 +1779,28 @@
         <v>27.3</v>
       </c>
       <c r="M6">
-        <v>1.2804368</v>
+        <v>1.600546</v>
       </c>
       <c r="N6">
-        <v>26.0195632</v>
+        <v>25.699454</v>
       </c>
       <c r="O6">
-        <v>2.60195632</v>
+        <v>2.5699454</v>
       </c>
       <c r="P6">
-        <v>23.41760688</v>
+        <v>23.1295086</v>
       </c>
       <c r="Q6">
-        <v>46.11760688</v>
+        <v>45.8295086</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1007846037889481</v>
+        <v>0.1013076025567567</v>
       </c>
       <c r="T6">
-        <v>0.8505943334155329</v>
+        <v>0.8586849580199926</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.32084926018996</v>
+        <v>17.05667940815196</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09850572242891885</v>
+        <v>0.09844742522044757</v>
       </c>
       <c r="C7">
-        <v>621.3004047372756</v>
+        <v>615.5693949694531</v>
       </c>
       <c r="D7">
-        <v>632.6204047372756</v>
+        <v>633.2533949694531</v>
       </c>
       <c r="E7">
-        <v>-22.38</v>
+        <v>-16.01599999999999</v>
       </c>
       <c r="F7">
-        <v>31.82000000000001</v>
+        <v>38.18400000000001</v>
       </c>
       <c r="G7">
         <v>20.5</v>
@@ -1861,28 +1861,28 @@
         <v>27.3</v>
       </c>
       <c r="M7">
-        <v>1.600546</v>
+        <v>1.920655200000001</v>
       </c>
       <c r="N7">
-        <v>25.699454</v>
+        <v>25.3793448</v>
       </c>
       <c r="O7">
-        <v>2.5699454</v>
+        <v>2.53793448</v>
       </c>
       <c r="P7">
-        <v>23.1295086</v>
+        <v>22.84141032</v>
       </c>
       <c r="Q7">
-        <v>45.8295086</v>
+        <v>45.54141032</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1013076025567567</v>
+        <v>0.101841728957923</v>
       </c>
       <c r="T7">
-        <v>0.8586849580199926</v>
+        <v>0.8669477235734834</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.05667940815196</v>
+        <v>14.2138995067933</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09844742522044757</v>
+        <v>0.09848362801197631</v>
       </c>
       <c r="C8">
-        <v>615.5693949694531</v>
+        <v>608.8121566176029</v>
       </c>
       <c r="D8">
-        <v>633.2533949694531</v>
+        <v>632.8601566176029</v>
       </c>
       <c r="E8">
-        <v>-16.016</v>
+        <v>-9.652000000000001</v>
       </c>
       <c r="F8">
-        <v>38.184</v>
+        <v>44.548</v>
       </c>
       <c r="G8">
         <v>20.5</v>
@@ -1943,45 +1943,45 @@
         <v>27.3</v>
       </c>
       <c r="M8">
-        <v>1.9206552</v>
+        <v>2.3075864</v>
       </c>
       <c r="N8">
-        <v>25.3793448</v>
+        <v>24.9924136</v>
       </c>
       <c r="O8">
-        <v>2.537934480000001</v>
+        <v>2.49924136</v>
       </c>
       <c r="P8">
-        <v>22.84141032</v>
+        <v>22.49317224</v>
       </c>
       <c r="Q8">
-        <v>45.54141032</v>
+        <v>45.19317224</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.101841728957923</v>
+        <v>0.1023873419483616</v>
       </c>
       <c r="T8">
-        <v>0.8669477235734834</v>
+        <v>0.8753881830098449</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.21389950679331</v>
+        <v>11.8305429430508</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09848362801197631</v>
+        <v>0.09843883080350505</v>
       </c>
       <c r="C9">
-        <v>608.8121566176029</v>
+        <v>602.9348201760034</v>
       </c>
       <c r="D9">
-        <v>632.8601566176029</v>
+        <v>633.3468201760035</v>
       </c>
       <c r="E9">
-        <v>-9.651999999999994</v>
+        <v>-3.287999999999997</v>
       </c>
       <c r="F9">
-        <v>44.54800000000001</v>
+        <v>50.91200000000001</v>
       </c>
       <c r="G9">
         <v>20.5</v>
@@ -2025,28 +2025,28 @@
         <v>27.3</v>
       </c>
       <c r="M9">
-        <v>2.3075864</v>
+        <v>2.6372416</v>
       </c>
       <c r="N9">
-        <v>24.9924136</v>
+        <v>24.6627584</v>
       </c>
       <c r="O9">
-        <v>2.49924136</v>
+        <v>2.46627584</v>
       </c>
       <c r="P9">
-        <v>22.49317224</v>
+        <v>22.19648256</v>
       </c>
       <c r="Q9">
-        <v>45.19317224</v>
+        <v>44.89648256</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1023873419483616</v>
+        <v>0.1029448160907663</v>
       </c>
       <c r="T9">
-        <v>0.875388183009845</v>
+        <v>0.8840121306948231</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.8305429430508</v>
+        <v>10.35172507516945</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09843883080350505</v>
+        <v>0.09853173359503375</v>
       </c>
       <c r="C10">
-        <v>602.9348201760034</v>
+        <v>595.5623839699499</v>
       </c>
       <c r="D10">
-        <v>633.3468201760035</v>
+        <v>632.3383839699499</v>
       </c>
       <c r="E10">
-        <v>-3.287999999999997</v>
+        <v>3.076000000000001</v>
       </c>
       <c r="F10">
-        <v>50.91200000000001</v>
+        <v>57.276</v>
       </c>
       <c r="G10">
         <v>20.5</v>
@@ -2107,45 +2107,45 @@
         <v>27.3</v>
       </c>
       <c r="M10">
-        <v>2.6372416</v>
+        <v>3.064266</v>
       </c>
       <c r="N10">
-        <v>24.6627584</v>
+        <v>24.235734</v>
       </c>
       <c r="O10">
-        <v>2.46627584</v>
+        <v>2.4235734</v>
       </c>
       <c r="P10">
-        <v>22.19648256</v>
+        <v>21.8121606</v>
       </c>
       <c r="Q10">
-        <v>44.89648256</v>
+        <v>44.5121606</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1029448160907663</v>
+        <v>0.103514542412125</v>
       </c>
       <c r="T10">
-        <v>0.8840121306948231</v>
+        <v>0.8928256156915588</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.1</v>
       </c>
       <c r="W10">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.35172507516945</v>
+        <v>8.909148226687893</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09853173359503375</v>
+        <v>0.0985022363865625</v>
       </c>
       <c r="C11">
-        <v>595.5623839699499</v>
+        <v>589.518220558605</v>
       </c>
       <c r="D11">
-        <v>632.3383839699499</v>
+        <v>632.658220558605</v>
       </c>
       <c r="E11">
-        <v>3.076000000000001</v>
+        <v>9.439999999999998</v>
       </c>
       <c r="F11">
-        <v>57.276</v>
+        <v>63.64</v>
       </c>
       <c r="G11">
         <v>20.5</v>
@@ -2189,28 +2189,28 @@
         <v>27.3</v>
       </c>
       <c r="M11">
-        <v>3.064266</v>
+        <v>3.40474</v>
       </c>
       <c r="N11">
-        <v>24.235734</v>
+        <v>23.89526</v>
       </c>
       <c r="O11">
-        <v>2.4235734</v>
+        <v>2.389526</v>
       </c>
       <c r="P11">
-        <v>21.8121606</v>
+        <v>21.505734</v>
       </c>
       <c r="Q11">
-        <v>44.5121606</v>
+        <v>44.205734</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.103514542412125</v>
+        <v>0.1040969293184028</v>
       </c>
       <c r="T11">
-        <v>0.8928256156915588</v>
+        <v>0.9018349559104446</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.909148226687893</v>
+        <v>8.018233404019103</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0985022363865625</v>
+        <v>0.0985519391780912</v>
       </c>
       <c r="C12">
-        <v>589.518220558605</v>
+        <v>582.6154825218541</v>
       </c>
       <c r="D12">
-        <v>632.658220558605</v>
+        <v>632.1194825218541</v>
       </c>
       <c r="E12">
-        <v>9.440000000000012</v>
+        <v>15.804</v>
       </c>
       <c r="F12">
-        <v>63.64000000000001</v>
+        <v>70.004</v>
       </c>
       <c r="G12">
         <v>20.5</v>
@@ -2271,45 +2271,45 @@
         <v>27.3</v>
       </c>
       <c r="M12">
-        <v>3.404740000000001</v>
+        <v>3.8012172</v>
       </c>
       <c r="N12">
-        <v>23.89526</v>
+        <v>23.4987828</v>
       </c>
       <c r="O12">
-        <v>2.389526</v>
+        <v>2.34987828</v>
       </c>
       <c r="P12">
-        <v>21.505734</v>
+        <v>21.14890452</v>
       </c>
       <c r="Q12">
-        <v>44.205734</v>
+        <v>43.84890452</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1040969293184028</v>
+        <v>0.104692403570889</v>
       </c>
       <c r="T12">
-        <v>0.9018349559104446</v>
+        <v>0.9110467532129004</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.018233404019101</v>
+        <v>7.181910047129114</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0985519391780912</v>
+        <v>0.09852964196961993</v>
       </c>
       <c r="C13">
-        <v>582.6154825218541</v>
+        <v>576.4930526950211</v>
       </c>
       <c r="D13">
-        <v>632.1194825218541</v>
+        <v>632.3610526950212</v>
       </c>
       <c r="E13">
-        <v>15.804</v>
+        <v>22.16800000000001</v>
       </c>
       <c r="F13">
-        <v>70.004</v>
+        <v>76.36800000000001</v>
       </c>
       <c r="G13">
         <v>20.5</v>
@@ -2353,28 +2353,28 @@
         <v>27.3</v>
       </c>
       <c r="M13">
-        <v>3.8012172</v>
+        <v>4.1467824</v>
       </c>
       <c r="N13">
-        <v>23.4987828</v>
+        <v>23.1532176</v>
       </c>
       <c r="O13">
-        <v>2.34987828</v>
+        <v>2.31532176</v>
       </c>
       <c r="P13">
-        <v>21.14890452</v>
+        <v>20.83789584</v>
       </c>
       <c r="Q13">
-        <v>43.84890452</v>
+        <v>43.53789584</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.104692403570889</v>
+        <v>0.1053014113291136</v>
       </c>
       <c r="T13">
-        <v>0.9110467532129004</v>
+        <v>0.9204679095449578</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.181910047129114</v>
+        <v>6.583417543201688</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09852964196961993</v>
+        <v>0.09862434476114866</v>
       </c>
       <c r="C14">
-        <v>576.4930526950211</v>
+        <v>569.1043044460454</v>
       </c>
       <c r="D14">
-        <v>632.3610526950212</v>
+        <v>631.3363044460453</v>
       </c>
       <c r="E14">
-        <v>22.16800000000001</v>
+        <v>28.53200000000001</v>
       </c>
       <c r="F14">
-        <v>76.36800000000001</v>
+        <v>82.73200000000001</v>
       </c>
       <c r="G14">
         <v>20.5</v>
@@ -2435,45 +2435,45 @@
         <v>27.3</v>
       </c>
       <c r="M14">
-        <v>4.1467824</v>
+        <v>4.5750796</v>
       </c>
       <c r="N14">
-        <v>23.1532176</v>
+        <v>22.7249204</v>
       </c>
       <c r="O14">
-        <v>2.31532176</v>
+        <v>2.27249204</v>
       </c>
       <c r="P14">
-        <v>20.83789584</v>
+        <v>20.45242836</v>
       </c>
       <c r="Q14">
-        <v>43.53789584</v>
+        <v>43.15242836</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1053014113291136</v>
+        <v>0.1059244192656881</v>
       </c>
       <c r="T14">
-        <v>0.9204679095449578</v>
+        <v>0.9301056441834991</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.583417543201688</v>
+        <v>5.967109293573821</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09862434476114866</v>
+        <v>0.09861104755267737</v>
       </c>
       <c r="C15">
-        <v>569.1043044460454</v>
+        <v>562.8839887606036</v>
       </c>
       <c r="D15">
-        <v>631.3363044460453</v>
+        <v>631.4799887606036</v>
       </c>
       <c r="E15">
-        <v>28.53200000000001</v>
+        <v>34.89600000000002</v>
       </c>
       <c r="F15">
-        <v>82.73200000000001</v>
+        <v>89.09600000000002</v>
       </c>
       <c r="G15">
         <v>20.5</v>
@@ -2517,28 +2517,28 @@
         <v>27.3</v>
       </c>
       <c r="M15">
-        <v>4.5750796</v>
+        <v>4.927008800000001</v>
       </c>
       <c r="N15">
-        <v>22.7249204</v>
+        <v>22.3729912</v>
       </c>
       <c r="O15">
-        <v>2.27249204</v>
+        <v>2.23729912</v>
       </c>
       <c r="P15">
-        <v>20.45242836</v>
+        <v>20.13569208</v>
       </c>
       <c r="Q15">
-        <v>43.15242836</v>
+        <v>42.83569208</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1059244192656881</v>
+        <v>0.1065619157589272</v>
       </c>
       <c r="T15">
-        <v>0.9301056441834991</v>
+        <v>0.9399675121857275</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.967109293573821</v>
+        <v>5.54088720117569</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09861104755267737</v>
+        <v>0.09859775034420611</v>
       </c>
       <c r="C16">
-        <v>562.8839887606036</v>
+        <v>556.6637384915861</v>
       </c>
       <c r="D16">
-        <v>631.4799887606036</v>
+        <v>631.6237384915861</v>
       </c>
       <c r="E16">
-        <v>34.89600000000002</v>
+        <v>41.26000000000002</v>
       </c>
       <c r="F16">
-        <v>89.09600000000002</v>
+        <v>95.46000000000002</v>
       </c>
       <c r="G16">
         <v>20.5</v>
@@ -2599,28 +2599,28 @@
         <v>27.3</v>
       </c>
       <c r="M16">
-        <v>4.927008800000001</v>
+        <v>5.278938000000001</v>
       </c>
       <c r="N16">
-        <v>22.3729912</v>
+        <v>22.021062</v>
       </c>
       <c r="O16">
-        <v>2.23729912</v>
+        <v>2.2021062</v>
       </c>
       <c r="P16">
-        <v>20.13569208</v>
+        <v>19.8189558</v>
       </c>
       <c r="Q16">
-        <v>42.83569208</v>
+        <v>42.5189558</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1065619157589272</v>
+        <v>0.1072144121696542</v>
       </c>
       <c r="T16">
-        <v>0.9399675121857275</v>
+        <v>0.9500614241409496</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.54088720117569</v>
+        <v>5.171494721097311</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09859775034420611</v>
+        <v>0.09858445313573484</v>
       </c>
       <c r="C17">
-        <v>556.6637384915861</v>
+        <v>550.4435536836777</v>
       </c>
       <c r="D17">
-        <v>631.6237384915861</v>
+        <v>631.7675536836776</v>
       </c>
       <c r="E17">
-        <v>41.26000000000001</v>
+        <v>47.62400000000001</v>
       </c>
       <c r="F17">
-        <v>95.46000000000001</v>
+        <v>101.824</v>
       </c>
       <c r="G17">
         <v>20.5</v>
@@ -2681,28 +2681,28 @@
         <v>27.3</v>
       </c>
       <c r="M17">
-        <v>5.278938000000001</v>
+        <v>5.630867200000001</v>
       </c>
       <c r="N17">
-        <v>22.021062</v>
+        <v>21.6691328</v>
       </c>
       <c r="O17">
-        <v>2.2021062</v>
+        <v>2.16691328</v>
       </c>
       <c r="P17">
-        <v>19.8189558</v>
+        <v>19.50221952</v>
       </c>
       <c r="Q17">
-        <v>42.5189558</v>
+        <v>42.20221952</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1072144121696542</v>
+        <v>0.1078824442092081</v>
       </c>
       <c r="T17">
-        <v>0.9500614241409496</v>
+        <v>0.9603956673332007</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.171494721097311</v>
+        <v>4.848276301028729</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09858445313573484</v>
+        <v>0.09857115592726354</v>
       </c>
       <c r="C18">
-        <v>550.4435536836777</v>
+        <v>544.2234343816035</v>
       </c>
       <c r="D18">
-        <v>631.7675536836776</v>
+        <v>631.9114343816035</v>
       </c>
       <c r="E18">
-        <v>47.62400000000001</v>
+        <v>53.98800000000001</v>
       </c>
       <c r="F18">
-        <v>101.824</v>
+        <v>108.188</v>
       </c>
       <c r="G18">
         <v>20.5</v>
@@ -2763,28 +2763,28 @@
         <v>27.3</v>
       </c>
       <c r="M18">
-        <v>5.630867200000001</v>
+        <v>5.982796400000002</v>
       </c>
       <c r="N18">
-        <v>21.6691328</v>
+        <v>21.3172036</v>
       </c>
       <c r="O18">
-        <v>2.16691328</v>
+        <v>2.13172036</v>
       </c>
       <c r="P18">
-        <v>19.50221952</v>
+        <v>19.18548324</v>
       </c>
       <c r="Q18">
-        <v>42.20221952</v>
+        <v>41.88548324</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1078824442092081</v>
+        <v>0.1085665734063416</v>
       </c>
       <c r="T18">
-        <v>0.9603956673332007</v>
+        <v>0.9709789284336987</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.848276301028729</v>
+        <v>4.563083577438803</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09857115592726354</v>
+        <v>0.09896285871879228</v>
       </c>
       <c r="C19">
-        <v>544.2234343816035</v>
+        <v>533.6483515980088</v>
       </c>
       <c r="D19">
-        <v>631.9114343816035</v>
+        <v>627.7003515980089</v>
       </c>
       <c r="E19">
-        <v>53.98800000000001</v>
+        <v>60.35200000000003</v>
       </c>
       <c r="F19">
-        <v>108.188</v>
+        <v>114.552</v>
       </c>
       <c r="G19">
         <v>20.5</v>
@@ -2845,45 +2845,45 @@
         <v>27.3</v>
       </c>
       <c r="M19">
-        <v>5.982796400000002</v>
+        <v>6.621105600000003</v>
       </c>
       <c r="N19">
-        <v>21.3172036</v>
+        <v>20.6788944</v>
       </c>
       <c r="O19">
-        <v>2.13172036</v>
+        <v>2.06788944</v>
       </c>
       <c r="P19">
-        <v>19.18548324</v>
+        <v>18.61100496</v>
       </c>
       <c r="Q19">
-        <v>41.88548324</v>
+        <v>41.31100496</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1085665734063416</v>
+        <v>0.109267388681454</v>
       </c>
       <c r="T19">
-        <v>0.9709789284336987</v>
+        <v>0.9818203178537211</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.563083577438803</v>
+        <v>4.123178461313167</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09896285871879229</v>
+        <v>0.09957056151032101</v>
       </c>
       <c r="C20">
-        <v>533.6483515980087</v>
+        <v>520.8610627850622</v>
       </c>
       <c r="D20">
-        <v>627.7003515980088</v>
+        <v>621.2770627850623</v>
       </c>
       <c r="E20">
-        <v>60.352</v>
+        <v>66.71600000000002</v>
       </c>
       <c r="F20">
-        <v>114.552</v>
+        <v>120.916</v>
       </c>
       <c r="G20">
         <v>20.5</v>
@@ -2927,45 +2927,45 @@
         <v>27.3</v>
       </c>
       <c r="M20">
-        <v>6.621105600000001</v>
+        <v>7.412150800000002</v>
       </c>
       <c r="N20">
-        <v>20.6788944</v>
+        <v>19.8878492</v>
       </c>
       <c r="O20">
-        <v>2.06788944</v>
+        <v>1.98878492</v>
       </c>
       <c r="P20">
-        <v>18.61100496</v>
+        <v>17.89906428</v>
       </c>
       <c r="Q20">
-        <v>41.31100496000001</v>
+        <v>40.59906427999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.109267388681454</v>
+        <v>0.1099855080374333</v>
       </c>
       <c r="T20">
-        <v>0.9818203178537211</v>
+        <v>0.9929293959013984</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.1</v>
       </c>
       <c r="W20">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.123178461313168</v>
+        <v>3.68314147089398</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09957056151032101</v>
+        <v>0.1001152643018497</v>
       </c>
       <c r="C21">
-        <v>520.8610627850622</v>
+        <v>508.8503787147499</v>
       </c>
       <c r="D21">
-        <v>621.2770627850623</v>
+        <v>615.6303787147499</v>
       </c>
       <c r="E21">
-        <v>66.71600000000002</v>
+        <v>73.08000000000003</v>
       </c>
       <c r="F21">
-        <v>120.916</v>
+        <v>127.28</v>
       </c>
       <c r="G21">
         <v>20.5</v>
@@ -3009,45 +3009,45 @@
         <v>27.3</v>
       </c>
       <c r="M21">
-        <v>7.412150800000002</v>
+        <v>8.158648000000003</v>
       </c>
       <c r="N21">
-        <v>19.8878492</v>
+        <v>19.141352</v>
       </c>
       <c r="O21">
-        <v>1.98878492</v>
+        <v>1.9141352</v>
       </c>
       <c r="P21">
-        <v>17.89906428</v>
+        <v>17.2272168</v>
       </c>
       <c r="Q21">
-        <v>40.59906427999999</v>
+        <v>39.9272168</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1099855080374333</v>
+        <v>0.1107215803773122</v>
       </c>
       <c r="T21">
-        <v>0.9929293959013984</v>
+        <v>1.004316200900268</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.68314147089398</v>
+        <v>3.346142645202979</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1001152643018497</v>
+        <v>0.1001811670933785</v>
       </c>
       <c r="C22">
-        <v>508.8503787147499</v>
+        <v>501.8101476542358</v>
       </c>
       <c r="D22">
-        <v>615.6303787147499</v>
+        <v>614.9541476542358</v>
       </c>
       <c r="E22">
-        <v>73.08000000000003</v>
+        <v>79.44400000000003</v>
       </c>
       <c r="F22">
-        <v>127.28</v>
+        <v>133.644</v>
       </c>
       <c r="G22">
         <v>20.5</v>
@@ -3091,28 +3091,28 @@
         <v>27.3</v>
       </c>
       <c r="M22">
-        <v>8.158648000000003</v>
+        <v>8.566580400000003</v>
       </c>
       <c r="N22">
-        <v>19.141352</v>
+        <v>18.7334196</v>
       </c>
       <c r="O22">
-        <v>1.9141352</v>
+        <v>1.87334196</v>
       </c>
       <c r="P22">
-        <v>17.2272168</v>
+        <v>16.86007764</v>
       </c>
       <c r="Q22">
-        <v>39.9272168</v>
+        <v>39.56007764</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1107215803773122</v>
+        <v>0.1114762874599727</v>
       </c>
       <c r="T22">
-        <v>1.004316200900268</v>
+        <v>1.015991279443412</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.346142645202979</v>
+        <v>3.186802519240932</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1001811670933785</v>
+        <v>0.1002470698849072</v>
       </c>
       <c r="C23">
-        <v>501.8101476542358</v>
+        <v>494.771400557839</v>
       </c>
       <c r="D23">
-        <v>614.9541476542358</v>
+        <v>614.279400557839</v>
       </c>
       <c r="E23">
-        <v>79.444</v>
+        <v>85.80800000000001</v>
       </c>
       <c r="F23">
-        <v>133.644</v>
+        <v>140.008</v>
       </c>
       <c r="G23">
         <v>20.5</v>
@@ -3173,28 +3173,28 @@
         <v>27.3</v>
       </c>
       <c r="M23">
-        <v>8.566580400000001</v>
+        <v>8.974512800000001</v>
       </c>
       <c r="N23">
-        <v>18.7334196</v>
+        <v>18.3254872</v>
       </c>
       <c r="O23">
-        <v>1.87334196</v>
+        <v>1.83254872</v>
       </c>
       <c r="P23">
-        <v>16.86007764</v>
+        <v>16.49293848</v>
       </c>
       <c r="Q23">
-        <v>39.56007764</v>
+        <v>39.19293848</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1114762874599727</v>
+        <v>0.1122503460062913</v>
       </c>
       <c r="T23">
-        <v>1.015991279443412</v>
+        <v>1.027965718974842</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.186802519240933</v>
+        <v>3.041947859275436</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1002470698849072</v>
+        <v>0.1019275726764359</v>
       </c>
       <c r="C24">
-        <v>494.771400557839</v>
+        <v>471.6882047523323</v>
       </c>
       <c r="D24">
-        <v>614.279400557839</v>
+        <v>597.5602047523323</v>
       </c>
       <c r="E24">
-        <v>85.80800000000001</v>
+        <v>92.17200000000001</v>
       </c>
       <c r="F24">
-        <v>140.008</v>
+        <v>146.372</v>
       </c>
       <c r="G24">
         <v>20.5</v>
@@ -3255,45 +3255,45 @@
         <v>27.3</v>
       </c>
       <c r="M24">
-        <v>8.974512800000001</v>
+        <v>10.5241468</v>
       </c>
       <c r="N24">
-        <v>18.3254872</v>
+        <v>16.7758532</v>
       </c>
       <c r="O24">
-        <v>1.83254872</v>
+        <v>1.67758532</v>
       </c>
       <c r="P24">
-        <v>16.49293848</v>
+        <v>15.09826788</v>
       </c>
       <c r="Q24">
-        <v>39.19293848</v>
+        <v>37.79826788</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1122503460062913</v>
+        <v>0.1130445099693973</v>
       </c>
       <c r="T24">
-        <v>1.027965718974842</v>
+        <v>1.040251182909686</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.1</v>
       </c>
       <c r="W24">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.041947859275436</v>
+        <v>2.594034511187168</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1019275726764359</v>
+        <v>0.1029060754679646</v>
       </c>
       <c r="C25">
-        <v>471.6882047523323</v>
+        <v>456.0018583874212</v>
       </c>
       <c r="D25">
-        <v>597.5602047523323</v>
+        <v>588.2378583874213</v>
       </c>
       <c r="E25">
-        <v>92.17200000000001</v>
+        <v>98.53600000000004</v>
       </c>
       <c r="F25">
-        <v>146.372</v>
+        <v>152.736</v>
       </c>
       <c r="G25">
         <v>20.5</v>
@@ -3337,45 +3337,45 @@
         <v>27.3</v>
       </c>
       <c r="M25">
-        <v>10.5241468</v>
+        <v>11.5773888</v>
       </c>
       <c r="N25">
-        <v>16.7758532</v>
+        <v>15.7226112</v>
       </c>
       <c r="O25">
-        <v>1.67758532</v>
+        <v>1.57226112</v>
       </c>
       <c r="P25">
-        <v>15.09826788</v>
+        <v>14.15035008</v>
       </c>
       <c r="Q25">
-        <v>37.79826788</v>
+        <v>36.85035008</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1130445099693973</v>
+        <v>0.113859572984164</v>
       </c>
       <c r="T25">
-        <v>1.040251182909686</v>
+        <v>1.052859948527026</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.1</v>
       </c>
       <c r="W25">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.594034511187168</v>
+        <v>2.358044674115115</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1029060754679646</v>
+        <v>0.1030772782594934</v>
       </c>
       <c r="C26">
-        <v>456.0018583874215</v>
+        <v>448.0365997151005</v>
       </c>
       <c r="D26">
-        <v>588.2378583874215</v>
+        <v>586.6365997151005</v>
       </c>
       <c r="E26">
-        <v>98.53600000000002</v>
+        <v>104.9</v>
       </c>
       <c r="F26">
-        <v>152.736</v>
+        <v>159.1</v>
       </c>
       <c r="G26">
         <v>20.5</v>
@@ -3419,28 +3419,28 @@
         <v>27.3</v>
       </c>
       <c r="M26">
-        <v>11.5773888</v>
+        <v>12.05978</v>
       </c>
       <c r="N26">
-        <v>15.7226112</v>
+        <v>15.24022</v>
       </c>
       <c r="O26">
-        <v>1.57226112</v>
+        <v>1.524022</v>
       </c>
       <c r="P26">
-        <v>14.15035008</v>
+        <v>13.716198</v>
       </c>
       <c r="Q26">
-        <v>36.85035008</v>
+        <v>36.41619799999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.113859572984164</v>
+        <v>0.1146963710126578</v>
       </c>
       <c r="T26">
-        <v>1.052859948527026</v>
+        <v>1.065804947894162</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.358044674115116</v>
+        <v>2.263722887150511</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1030772782594934</v>
+        <v>0.1032484810510221</v>
       </c>
       <c r="C27">
-        <v>448.0365997151005</v>
+        <v>440.0800350383503</v>
       </c>
       <c r="D27">
-        <v>586.6365997151005</v>
+        <v>585.0440350383503</v>
       </c>
       <c r="E27">
-        <v>104.9</v>
+        <v>111.264</v>
       </c>
       <c r="F27">
-        <v>159.1</v>
+        <v>165.464</v>
       </c>
       <c r="G27">
         <v>20.5</v>
@@ -3501,28 +3501,28 @@
         <v>27.3</v>
       </c>
       <c r="M27">
-        <v>12.05978</v>
+        <v>12.5421712</v>
       </c>
       <c r="N27">
-        <v>15.24022</v>
+        <v>14.7578288</v>
       </c>
       <c r="O27">
-        <v>1.524022</v>
+        <v>1.47578288</v>
       </c>
       <c r="P27">
-        <v>13.716198</v>
+        <v>13.28204592</v>
       </c>
       <c r="Q27">
-        <v>36.41619799999999</v>
+        <v>35.98204592</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1146963710126578</v>
+        <v>0.1155557852040839</v>
       </c>
       <c r="T27">
-        <v>1.065804947894162</v>
+        <v>1.079099812109058</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.263722887150511</v>
+        <v>2.176656622260107</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1032484810510221</v>
+        <v>0.1034196838425508</v>
       </c>
       <c r="C28">
-        <v>440.0800350383503</v>
+        <v>432.1320937431095</v>
       </c>
       <c r="D28">
-        <v>585.0440350383503</v>
+        <v>583.4600937431095</v>
       </c>
       <c r="E28">
-        <v>111.264</v>
+        <v>117.628</v>
       </c>
       <c r="F28">
-        <v>165.464</v>
+        <v>171.828</v>
       </c>
       <c r="G28">
         <v>20.5</v>
@@ -3583,28 +3583,28 @@
         <v>27.3</v>
       </c>
       <c r="M28">
-        <v>12.5421712</v>
+        <v>13.0245624</v>
       </c>
       <c r="N28">
-        <v>14.7578288</v>
+        <v>14.2754376</v>
       </c>
       <c r="O28">
-        <v>1.47578288</v>
+        <v>1.42754376</v>
       </c>
       <c r="P28">
-        <v>13.28204592</v>
+        <v>12.84789384</v>
       </c>
       <c r="Q28">
-        <v>35.98204592</v>
+        <v>35.54789384</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1155557852040839</v>
+        <v>0.1164387449897956</v>
       </c>
       <c r="T28">
-        <v>1.079099812109058</v>
+        <v>1.092758919179156</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.176656622260107</v>
+        <v>2.096039710324547</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1034196838425508</v>
+        <v>0.1035908866340795</v>
       </c>
       <c r="C29">
-        <v>432.1320937431095</v>
+        <v>424.1927059779695</v>
       </c>
       <c r="D29">
-        <v>583.4600937431095</v>
+        <v>581.8847059779695</v>
       </c>
       <c r="E29">
-        <v>117.628</v>
+        <v>123.992</v>
       </c>
       <c r="F29">
-        <v>171.828</v>
+        <v>178.192</v>
       </c>
       <c r="G29">
         <v>20.5</v>
@@ -3665,28 +3665,28 @@
         <v>27.3</v>
       </c>
       <c r="M29">
-        <v>13.0245624</v>
+        <v>13.5069536</v>
       </c>
       <c r="N29">
-        <v>14.2754376</v>
+        <v>13.7930464</v>
       </c>
       <c r="O29">
-        <v>1.42754376</v>
+        <v>1.37930464</v>
       </c>
       <c r="P29">
-        <v>12.84789384</v>
+        <v>12.41374176</v>
       </c>
       <c r="Q29">
-        <v>35.54789384</v>
+        <v>35.11374176</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1164387449897956</v>
+        <v>0.1173462314362216</v>
       </c>
       <c r="T29">
-        <v>1.092758919179156</v>
+        <v>1.106797445890091</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.096039710324547</v>
+        <v>2.021181149241528</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1035908866340795</v>
+        <v>0.1074682894256083</v>
       </c>
       <c r="C30">
-        <v>424.1927059779695</v>
+        <v>384.296202381106</v>
       </c>
       <c r="D30">
-        <v>581.8847059779695</v>
+        <v>548.3522023811061</v>
       </c>
       <c r="E30">
-        <v>123.992</v>
+        <v>130.3560000000001</v>
       </c>
       <c r="F30">
-        <v>178.192</v>
+        <v>184.556</v>
       </c>
       <c r="G30">
         <v>20.5</v>
@@ -3747,45 +3747,45 @@
         <v>27.3</v>
       </c>
       <c r="M30">
-        <v>13.5069536</v>
+        <v>16.61004</v>
       </c>
       <c r="N30">
-        <v>13.7930464</v>
+        <v>10.68996</v>
       </c>
       <c r="O30">
-        <v>1.37930464</v>
+        <v>1.068996</v>
       </c>
       <c r="P30">
-        <v>12.41374176</v>
+        <v>9.620963999999999</v>
       </c>
       <c r="Q30">
-        <v>35.11374176</v>
+        <v>32.320964</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1173462314362216</v>
+        <v>0.1182792808811384</v>
       </c>
       <c r="T30">
-        <v>1.106797445890091</v>
+        <v>1.121231424057672</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.021181149241528</v>
+        <v>1.643584241820008</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1074682894256083</v>
+        <v>0.107767292217137</v>
       </c>
       <c r="C31">
-        <v>384.2962023811061</v>
+        <v>375.5061662074561</v>
       </c>
       <c r="D31">
-        <v>548.3522023811062</v>
+        <v>545.9261662074562</v>
       </c>
       <c r="E31">
-        <v>130.356</v>
+        <v>136.72</v>
       </c>
       <c r="F31">
-        <v>184.556</v>
+        <v>190.92</v>
       </c>
       <c r="G31">
         <v>20.5</v>
@@ -3829,28 +3829,28 @@
         <v>27.3</v>
       </c>
       <c r="M31">
-        <v>16.61004</v>
+        <v>17.1828</v>
       </c>
       <c r="N31">
-        <v>10.68996</v>
+        <v>10.1172</v>
       </c>
       <c r="O31">
-        <v>1.068996</v>
+        <v>1.01172</v>
       </c>
       <c r="P31">
-        <v>9.620963999999999</v>
+        <v>9.10548</v>
       </c>
       <c r="Q31">
-        <v>32.320964</v>
+        <v>31.80548</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1182792808811384</v>
+        <v>0.1192389888816243</v>
       </c>
       <c r="T31">
-        <v>1.121231424057672</v>
+        <v>1.136077801601469</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.643584241820008</v>
+        <v>1.588798100426007</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.107767292217137</v>
+        <v>0.1080662950086657</v>
       </c>
       <c r="C32">
-        <v>375.5061662074561</v>
+        <v>366.7375021618381</v>
       </c>
       <c r="D32">
-        <v>545.9261662074562</v>
+        <v>543.521502161838</v>
       </c>
       <c r="E32">
-        <v>136.72</v>
+        <v>143.084</v>
       </c>
       <c r="F32">
-        <v>190.92</v>
+        <v>197.284</v>
       </c>
       <c r="G32">
         <v>20.5</v>
@@ -3911,28 +3911,28 @@
         <v>27.3</v>
       </c>
       <c r="M32">
-        <v>17.1828</v>
+        <v>17.75556</v>
       </c>
       <c r="N32">
-        <v>10.1172</v>
+        <v>9.544439999999998</v>
       </c>
       <c r="O32">
-        <v>1.01172</v>
+        <v>0.9544439999999998</v>
       </c>
       <c r="P32">
-        <v>9.10548</v>
+        <v>8.589995999999998</v>
       </c>
       <c r="Q32">
-        <v>31.80548</v>
+        <v>31.289996</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1192389888816243</v>
+        <v>0.1202265145053126</v>
       </c>
       <c r="T32">
-        <v>1.136077801601469</v>
+        <v>1.151354508929145</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.588798100426007</v>
+        <v>1.537546548799362</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1080662950086657</v>
+        <v>0.125278781711862</v>
       </c>
       <c r="C33">
-        <v>366.7375021618381</v>
+        <v>250.4327171706802</v>
       </c>
       <c r="D33">
-        <v>543.521502161838</v>
+        <v>433.5807171706802</v>
       </c>
       <c r="E33">
-        <v>143.084</v>
+        <v>149.448</v>
       </c>
       <c r="F33">
-        <v>197.284</v>
+        <v>203.648</v>
       </c>
       <c r="G33">
         <v>20.5</v>
@@ -3993,45 +3993,45 @@
         <v>27.3</v>
       </c>
       <c r="M33">
-        <v>17.75556</v>
+        <v>29.8955264</v>
       </c>
       <c r="N33">
-        <v>9.544439999999998</v>
+        <v>-2.595526400000004</v>
       </c>
       <c r="O33">
-        <v>0.9544439999999998</v>
+        <v>-0.2595526400000004</v>
       </c>
       <c r="P33">
-        <v>8.589995999999998</v>
+        <v>-2.335973760000004</v>
       </c>
       <c r="Q33">
-        <v>31.289996</v>
+        <v>20.36402623999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1202265145053126</v>
+        <v>0.1214596126220767</v>
       </c>
       <c r="T33">
-        <v>1.151354508929145</v>
+        <v>1.170430144623291</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.1</v>
+        <v>0.09131801071079317</v>
       </c>
       <c r="W33">
-        <v>0.081</v>
+        <v>0.1333945160276556</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.537546548799362</v>
+        <v>0.9131801071079316</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.125278781711862</v>
+        <v>0.126288781711862</v>
       </c>
       <c r="C34">
-        <v>250.4327171706802</v>
+        <v>238.9828447575965</v>
       </c>
       <c r="D34">
-        <v>433.5807171706802</v>
+        <v>428.4948447575965</v>
       </c>
       <c r="E34">
-        <v>149.448</v>
+        <v>155.812</v>
       </c>
       <c r="F34">
-        <v>203.648</v>
+        <v>210.012</v>
       </c>
       <c r="G34">
         <v>20.5</v>
@@ -4075,37 +4075,37 @@
         <v>27.3</v>
       </c>
       <c r="M34">
-        <v>29.8955264</v>
+        <v>30.82976160000001</v>
       </c>
       <c r="N34">
-        <v>-2.595526400000004</v>
+        <v>-3.529761600000008</v>
       </c>
       <c r="O34">
-        <v>-0.2595526400000004</v>
+        <v>-0.3529761600000008</v>
       </c>
       <c r="P34">
-        <v>-2.335973760000004</v>
+        <v>-3.176785440000007</v>
       </c>
       <c r="Q34">
-        <v>20.36402623999999</v>
+        <v>19.52321455999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1214596126220767</v>
+        <v>0.12258886057166</v>
       </c>
       <c r="T34">
-        <v>1.170430144623291</v>
+        <v>1.187899251259459</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.09131801071079317</v>
+        <v>0.08855079826501155</v>
       </c>
       <c r="W34">
-        <v>0.1333945160276556</v>
+        <v>0.1338007428146963</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9131801071079316</v>
+        <v>0.8855079826501153</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.126288781711862</v>
+        <v>0.127298781711862</v>
       </c>
       <c r="C35">
-        <v>238.9828447575965</v>
+        <v>227.6509029041515</v>
       </c>
       <c r="D35">
-        <v>428.4948447575965</v>
+        <v>423.5269029041515</v>
       </c>
       <c r="E35">
-        <v>155.812</v>
+        <v>162.176</v>
       </c>
       <c r="F35">
-        <v>210.012</v>
+        <v>216.376</v>
       </c>
       <c r="G35">
         <v>20.5</v>
@@ -4157,37 +4157,37 @@
         <v>27.3</v>
       </c>
       <c r="M35">
-        <v>30.82976160000001</v>
+        <v>31.76399680000001</v>
       </c>
       <c r="N35">
-        <v>-3.529761600000008</v>
+        <v>-4.463996800000007</v>
       </c>
       <c r="O35">
-        <v>-0.3529761600000008</v>
+        <v>-0.4463996800000007</v>
       </c>
       <c r="P35">
-        <v>-3.176785440000007</v>
+        <v>-4.017597120000007</v>
       </c>
       <c r="Q35">
-        <v>19.52321455999999</v>
+        <v>18.68240287999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.12258886057166</v>
+        <v>0.1237523281560791</v>
       </c>
       <c r="T35">
-        <v>1.187899251259459</v>
+        <v>1.20589772476339</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.08855079826501155</v>
+        <v>0.08594636302192298</v>
       </c>
       <c r="W35">
-        <v>0.1338007428146963</v>
+        <v>0.1341830739083817</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8855079826501153</v>
+        <v>0.8594636302192297</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.127298781711862</v>
+        <v>0.128308781711862</v>
       </c>
       <c r="C36">
-        <v>227.6509029041515</v>
+        <v>216.4328367836252</v>
       </c>
       <c r="D36">
-        <v>423.5269029041515</v>
+        <v>418.6728367836253</v>
       </c>
       <c r="E36">
-        <v>162.176</v>
+        <v>168.5400000000001</v>
       </c>
       <c r="F36">
-        <v>216.376</v>
+        <v>222.7400000000001</v>
       </c>
       <c r="G36">
         <v>20.5</v>
@@ -4239,37 +4239,37 @@
         <v>27.3</v>
       </c>
       <c r="M36">
-        <v>31.76399680000001</v>
+        <v>32.69823200000001</v>
       </c>
       <c r="N36">
-        <v>-4.463996800000007</v>
+        <v>-5.398232000000011</v>
       </c>
       <c r="O36">
-        <v>-0.4463996800000007</v>
+        <v>-0.5398232000000011</v>
       </c>
       <c r="P36">
-        <v>-4.017597120000007</v>
+        <v>-4.85840880000001</v>
       </c>
       <c r="Q36">
-        <v>18.68240287999999</v>
+        <v>17.84159119999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1237523281560791</v>
+        <v>0.1249515947430957</v>
       </c>
       <c r="T36">
-        <v>1.20589772476339</v>
+        <v>1.224449997452058</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.08594636302192298</v>
+        <v>0.08349075264986802</v>
       </c>
       <c r="W36">
-        <v>0.1341830739083817</v>
+        <v>0.1345435575109994</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8594636302192297</v>
+        <v>0.8349075264986802</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.128308781711862</v>
+        <v>0.129318781711862</v>
       </c>
       <c r="C37">
-        <v>216.4328367836252</v>
+        <v>205.3247753533452</v>
       </c>
       <c r="D37">
-        <v>418.6728367836253</v>
+        <v>413.9287753533453</v>
       </c>
       <c r="E37">
-        <v>168.5400000000001</v>
+        <v>174.9040000000001</v>
       </c>
       <c r="F37">
-        <v>222.7400000000001</v>
+        <v>229.1040000000001</v>
       </c>
       <c r="G37">
         <v>20.5</v>
@@ -4321,37 +4321,37 @@
         <v>27.3</v>
       </c>
       <c r="M37">
-        <v>32.69823200000001</v>
+        <v>33.63246720000001</v>
       </c>
       <c r="N37">
-        <v>-5.398232000000011</v>
+        <v>-6.332467200000014</v>
       </c>
       <c r="O37">
-        <v>-0.5398232000000011</v>
+        <v>-0.6332467200000015</v>
       </c>
       <c r="P37">
-        <v>-4.85840880000001</v>
+        <v>-5.699220480000013</v>
       </c>
       <c r="Q37">
-        <v>17.84159119999999</v>
+        <v>17.00077951999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1249515947430957</v>
+        <v>0.1261883384109565</v>
       </c>
       <c r="T37">
-        <v>1.224449997452058</v>
+        <v>1.243582028662246</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.08349075264986802</v>
+        <v>0.08117156507626057</v>
       </c>
       <c r="W37">
-        <v>0.1345435575109994</v>
+        <v>0.134884014246805</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8349075264986802</v>
+        <v>0.8117156507626057</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.129318781711862</v>
+        <v>0.1507252572196618</v>
       </c>
       <c r="C38">
-        <v>205.3247753533453</v>
+        <v>118.8026639742429</v>
       </c>
       <c r="D38">
-        <v>413.9287753533453</v>
+        <v>333.770663974243</v>
       </c>
       <c r="E38">
-        <v>174.904</v>
+        <v>181.268</v>
       </c>
       <c r="F38">
-        <v>229.104</v>
+        <v>235.468</v>
       </c>
       <c r="G38">
         <v>20.5</v>
@@ -4403,45 +4403,45 @@
         <v>27.3</v>
       </c>
       <c r="M38">
-        <v>33.63246720000001</v>
+        <v>47.2819744</v>
       </c>
       <c r="N38">
-        <v>-6.332467200000007</v>
+        <v>-19.9819744</v>
       </c>
       <c r="O38">
-        <v>-0.6332467200000007</v>
+        <v>-1.99819744</v>
       </c>
       <c r="P38">
-        <v>-5.699220480000006</v>
+        <v>-17.98377696</v>
       </c>
       <c r="Q38">
-        <v>17.00077951999999</v>
+        <v>4.716223039999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1261883384109565</v>
+        <v>0.1281254160171619</v>
       </c>
       <c r="T38">
-        <v>1.243582028662246</v>
+        <v>1.273548003165742</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.08117156507626058</v>
+        <v>0.0577387055985547</v>
       </c>
       <c r="W38">
-        <v>0.134884014246805</v>
+        <v>0.1892060679158102</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8117156507626058</v>
+        <v>0.577387055985547</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1507252572196618</v>
+        <v>0.1522752572196618</v>
       </c>
       <c r="C39">
-        <v>118.8026639742429</v>
+        <v>107.8232655819293</v>
       </c>
       <c r="D39">
-        <v>333.770663974243</v>
+        <v>329.1552655819293</v>
       </c>
       <c r="E39">
-        <v>181.268</v>
+        <v>187.6320000000001</v>
       </c>
       <c r="F39">
-        <v>235.468</v>
+        <v>241.8320000000001</v>
       </c>
       <c r="G39">
         <v>20.5</v>
@@ -4485,37 +4485,37 @@
         <v>27.3</v>
       </c>
       <c r="M39">
-        <v>47.2819744</v>
+        <v>48.55986560000001</v>
       </c>
       <c r="N39">
-        <v>-19.9819744</v>
+        <v>-21.25986560000001</v>
       </c>
       <c r="O39">
-        <v>-1.99819744</v>
+        <v>-2.125986560000001</v>
       </c>
       <c r="P39">
-        <v>-17.98377696</v>
+        <v>-19.13387904000001</v>
       </c>
       <c r="Q39">
-        <v>4.716223039999999</v>
+        <v>3.566120959999992</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1281254160171619</v>
+        <v>0.1294532453077613</v>
       </c>
       <c r="T39">
-        <v>1.273548003165742</v>
+        <v>1.294089099990996</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.0577387055985547</v>
+        <v>0.05621926597754009</v>
       </c>
       <c r="W39">
-        <v>0.1892060679158102</v>
+        <v>0.1895111713917099</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.577387055985547</v>
+        <v>0.562192659775401</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1522752572196618</v>
+        <v>0.1538252572196618</v>
       </c>
       <c r="C40">
-        <v>107.8232655819293</v>
+        <v>96.96977014301032</v>
       </c>
       <c r="D40">
-        <v>329.1552655819293</v>
+        <v>324.6657701430104</v>
       </c>
       <c r="E40">
-        <v>187.6320000000001</v>
+        <v>193.996</v>
       </c>
       <c r="F40">
-        <v>241.8320000000001</v>
+        <v>248.1960000000001</v>
       </c>
       <c r="G40">
         <v>20.5</v>
@@ -4567,37 +4567,37 @@
         <v>27.3</v>
       </c>
       <c r="M40">
-        <v>48.55986560000001</v>
+        <v>49.83775680000002</v>
       </c>
       <c r="N40">
-        <v>-21.25986560000001</v>
+        <v>-22.53775680000001</v>
       </c>
       <c r="O40">
-        <v>-2.125986560000001</v>
+        <v>-2.253775680000002</v>
       </c>
       <c r="P40">
-        <v>-19.13387904000001</v>
+        <v>-20.28398112000001</v>
       </c>
       <c r="Q40">
-        <v>3.566120959999992</v>
+        <v>2.416018879999985</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1294532453077613</v>
+        <v>0.1308246099849377</v>
       </c>
       <c r="T40">
-        <v>1.294089099990996</v>
+        <v>1.315303675400684</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05621926597754009</v>
+        <v>0.05477774633709034</v>
       </c>
       <c r="W40">
-        <v>0.1895111713917099</v>
+        <v>0.1898006285355123</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.562192659775401</v>
+        <v>0.5477774633709034</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1538252572196618</v>
+        <v>0.1553752572196618</v>
       </c>
       <c r="C41">
-        <v>96.96977014301032</v>
+        <v>86.23709523928818</v>
       </c>
       <c r="D41">
-        <v>324.6657701430104</v>
+        <v>320.2970952392882</v>
       </c>
       <c r="E41">
-        <v>193.996</v>
+        <v>200.3600000000001</v>
       </c>
       <c r="F41">
-        <v>248.1960000000001</v>
+        <v>254.5600000000001</v>
       </c>
       <c r="G41">
         <v>20.5</v>
@@ -4649,37 +4649,37 @@
         <v>27.3</v>
       </c>
       <c r="M41">
-        <v>49.83775680000002</v>
+        <v>51.11564800000001</v>
       </c>
       <c r="N41">
-        <v>-22.53775680000001</v>
+        <v>-23.81564800000001</v>
       </c>
       <c r="O41">
-        <v>-2.253775680000002</v>
+        <v>-2.381564800000001</v>
       </c>
       <c r="P41">
-        <v>-20.28398112000001</v>
+        <v>-21.43408320000001</v>
       </c>
       <c r="Q41">
-        <v>2.416018879999985</v>
+        <v>1.265916799999989</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1308246099849377</v>
+        <v>0.13224168681802</v>
       </c>
       <c r="T41">
-        <v>1.315303675400684</v>
+        <v>1.337225403324029</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05477774633709034</v>
+        <v>0.05340830267866309</v>
       </c>
       <c r="W41">
-        <v>0.1898006285355123</v>
+        <v>0.1900756128221245</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5477774633709034</v>
+        <v>0.5340830267866308</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1553752572196618</v>
+        <v>0.1569252572196618</v>
       </c>
       <c r="C42">
-        <v>86.23709523928818</v>
+        <v>75.62042837485626</v>
       </c>
       <c r="D42">
-        <v>320.2970952392882</v>
+        <v>316.0444283748563</v>
       </c>
       <c r="E42">
-        <v>200.3600000000001</v>
+        <v>206.724</v>
       </c>
       <c r="F42">
-        <v>254.5600000000001</v>
+        <v>260.924</v>
       </c>
       <c r="G42">
         <v>20.5</v>
@@ -4731,37 +4731,37 @@
         <v>27.3</v>
       </c>
       <c r="M42">
-        <v>51.11564800000001</v>
+        <v>52.39353920000001</v>
       </c>
       <c r="N42">
-        <v>-23.81564800000001</v>
+        <v>-25.09353920000001</v>
       </c>
       <c r="O42">
-        <v>-2.381564800000001</v>
+        <v>-2.509353920000001</v>
       </c>
       <c r="P42">
-        <v>-21.43408320000001</v>
+        <v>-22.58418528000001</v>
       </c>
       <c r="Q42">
-        <v>1.265916799999989</v>
+        <v>0.1158147199999924</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.13224168681802</v>
+        <v>0.1337068001539187</v>
       </c>
       <c r="T42">
-        <v>1.337225403324029</v>
+        <v>1.359890240668504</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05340830267866309</v>
+        <v>0.05210566114991522</v>
       </c>
       <c r="W42">
-        <v>0.1900756128221245</v>
+        <v>0.190337183241097</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5340830267866308</v>
+        <v>0.5210566114991522</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1569252572196618</v>
+        <v>0.1584752572196618</v>
       </c>
       <c r="C43">
-        <v>75.62042837485626</v>
+        <v>65.11520929176049</v>
       </c>
       <c r="D43">
-        <v>316.0444283748563</v>
+        <v>311.9032092917606</v>
       </c>
       <c r="E43">
-        <v>206.724</v>
+        <v>213.0880000000001</v>
       </c>
       <c r="F43">
-        <v>260.924</v>
+        <v>267.2880000000001</v>
       </c>
       <c r="G43">
         <v>20.5</v>
@@ -4813,37 +4813,37 @@
         <v>27.3</v>
       </c>
       <c r="M43">
-        <v>52.39353920000001</v>
+        <v>53.67143040000001</v>
       </c>
       <c r="N43">
-        <v>-25.09353920000001</v>
+        <v>-26.37143040000001</v>
       </c>
       <c r="O43">
-        <v>-2.509353920000001</v>
+        <v>-2.637143040000002</v>
       </c>
       <c r="P43">
-        <v>-22.58418528000001</v>
+        <v>-23.73428736000001</v>
       </c>
       <c r="Q43">
-        <v>0.1158147199999924</v>
+        <v>-1.034287360000011</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1337068001539187</v>
+        <v>0.1352224346393311</v>
       </c>
       <c r="T43">
-        <v>1.359890240668504</v>
+        <v>1.383336624128306</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05210566114991522</v>
+        <v>0.05086505017015533</v>
       </c>
       <c r="W43">
-        <v>0.190337183241097</v>
+        <v>0.1905862979258328</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5210566114991522</v>
+        <v>0.5086505017015532</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1584752572196618</v>
+        <v>0.1752433101175253</v>
       </c>
       <c r="C44">
-        <v>65.11520929176072</v>
+        <v>20.02733131120641</v>
       </c>
       <c r="D44">
-        <v>311.9032092917607</v>
+        <v>273.1793313112065</v>
       </c>
       <c r="E44">
-        <v>213.088</v>
+        <v>219.4520000000001</v>
       </c>
       <c r="F44">
-        <v>267.288</v>
+        <v>273.652</v>
       </c>
       <c r="G44">
         <v>20.5</v>
@@ -4895,45 +4895,45 @@
         <v>27.3</v>
       </c>
       <c r="M44">
-        <v>53.67143040000001</v>
+        <v>64.52714160000001</v>
       </c>
       <c r="N44">
-        <v>-26.3714304</v>
+        <v>-37.22714160000001</v>
       </c>
       <c r="O44">
-        <v>-2.637143040000001</v>
+        <v>-3.722714160000001</v>
       </c>
       <c r="P44">
-        <v>-23.73428736</v>
+        <v>-33.50442744000001</v>
       </c>
       <c r="Q44">
-        <v>-1.034287360000004</v>
+        <v>-10.80442744000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.135222434639331</v>
+        <v>0.1370860789275009</v>
       </c>
       <c r="T44">
-        <v>1.383336624128305</v>
+        <v>1.412166608556385</v>
       </c>
       <c r="U44">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.05086505017015533</v>
+        <v>0.04230777828224767</v>
       </c>
       <c r="W44">
-        <v>0.1905862979258328</v>
+        <v>0.225823825881046</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5086505017015532</v>
+        <v>0.4230777828224765</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1752433101175253</v>
+        <v>0.1771433101175253</v>
       </c>
       <c r="C45">
-        <v>20.02733131120641</v>
+        <v>9.873579600179255</v>
       </c>
       <c r="D45">
-        <v>273.1793313112065</v>
+        <v>269.3895796001793</v>
       </c>
       <c r="E45">
-        <v>219.4520000000001</v>
+        <v>225.816</v>
       </c>
       <c r="F45">
-        <v>273.652</v>
+        <v>280.016</v>
       </c>
       <c r="G45">
         <v>20.5</v>
@@ -4977,37 +4977,37 @@
         <v>27.3</v>
       </c>
       <c r="M45">
-        <v>64.52714160000001</v>
+        <v>66.02777280000001</v>
       </c>
       <c r="N45">
-        <v>-37.22714160000001</v>
+        <v>-38.72777280000001</v>
       </c>
       <c r="O45">
-        <v>-3.722714160000001</v>
+        <v>-3.872777280000001</v>
       </c>
       <c r="P45">
-        <v>-33.50442744000001</v>
+        <v>-34.85499552000001</v>
       </c>
       <c r="Q45">
-        <v>-10.80442744000001</v>
+        <v>-12.15499552000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1370860789275009</v>
+        <v>0.1387161874797777</v>
       </c>
       <c r="T45">
-        <v>1.412166608556385</v>
+        <v>1.437383869423463</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04230777828224767</v>
+        <v>0.04134623786674204</v>
       </c>
       <c r="W45">
-        <v>0.225823825881046</v>
+        <v>0.2260505571110222</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4230777828224765</v>
+        <v>0.4134623786674203</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1771433101175253</v>
+        <v>0.1790433101175253</v>
       </c>
       <c r="C46">
-        <v>9.873579600179255</v>
+        <v>-0.1764622102734279</v>
       </c>
       <c r="D46">
-        <v>269.3895796001793</v>
+        <v>265.7035377897266</v>
       </c>
       <c r="E46">
-        <v>225.816</v>
+        <v>232.1800000000001</v>
       </c>
       <c r="F46">
-        <v>280.016</v>
+        <v>286.3800000000001</v>
       </c>
       <c r="G46">
         <v>20.5</v>
@@ -5059,37 +5059,37 @@
         <v>27.3</v>
       </c>
       <c r="M46">
-        <v>66.02777280000001</v>
+        <v>67.52840400000001</v>
       </c>
       <c r="N46">
-        <v>-38.72777280000001</v>
+        <v>-40.22840400000001</v>
       </c>
       <c r="O46">
-        <v>-3.872777280000001</v>
+        <v>-4.022840400000002</v>
       </c>
       <c r="P46">
-        <v>-34.85499552000001</v>
+        <v>-36.20556360000001</v>
       </c>
       <c r="Q46">
-        <v>-12.15499552000001</v>
+        <v>-13.50556360000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1387161874797777</v>
+        <v>0.1404055727066827</v>
       </c>
       <c r="T46">
-        <v>1.437383869423463</v>
+        <v>1.463518121594799</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04134623786674204</v>
+        <v>0.04042743258081444</v>
       </c>
       <c r="W46">
-        <v>0.2260505571110222</v>
+        <v>0.226267211397444</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4134623786674203</v>
+        <v>0.4042743258081443</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1790433101175253</v>
+        <v>0.1809433101175253</v>
       </c>
       <c r="C47">
-        <v>-0.1764622102734279</v>
+        <v>-10.12699382528473</v>
       </c>
       <c r="D47">
-        <v>265.7035377897266</v>
+        <v>262.1170061747153</v>
       </c>
       <c r="E47">
-        <v>232.1800000000001</v>
+        <v>238.544</v>
       </c>
       <c r="F47">
-        <v>286.3800000000001</v>
+        <v>292.744</v>
       </c>
       <c r="G47">
         <v>20.5</v>
@@ -5141,37 +5141,37 @@
         <v>27.3</v>
       </c>
       <c r="M47">
-        <v>67.52840400000001</v>
+        <v>69.02903520000001</v>
       </c>
       <c r="N47">
-        <v>-40.22840400000001</v>
+        <v>-41.72903520000001</v>
       </c>
       <c r="O47">
-        <v>-4.022840400000002</v>
+        <v>-4.172903520000001</v>
       </c>
       <c r="P47">
-        <v>-36.20556360000001</v>
+        <v>-37.55613168000001</v>
       </c>
       <c r="Q47">
-        <v>-13.50556360000001</v>
+        <v>-14.85613168000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1404055727066827</v>
+        <v>0.1421575277568065</v>
       </c>
       <c r="T47">
-        <v>1.463518121594799</v>
+        <v>1.49062030903174</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04042743258081444</v>
+        <v>0.03954857535079673</v>
       </c>
       <c r="W47">
-        <v>0.226267211397444</v>
+        <v>0.2264744459322821</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4042743258081443</v>
+        <v>0.3954857535079672</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1809433101175253</v>
+        <v>0.1828433101175253</v>
       </c>
       <c r="C48">
-        <v>-10.12699382528473</v>
+        <v>-19.98199121540694</v>
       </c>
       <c r="D48">
-        <v>262.1170061747153</v>
+        <v>258.6260087845931</v>
       </c>
       <c r="E48">
-        <v>238.544</v>
+        <v>244.9080000000001</v>
       </c>
       <c r="F48">
-        <v>292.744</v>
+        <v>299.1080000000001</v>
       </c>
       <c r="G48">
         <v>20.5</v>
@@ -5223,37 +5223,37 @@
         <v>27.3</v>
       </c>
       <c r="M48">
-        <v>69.02903520000001</v>
+        <v>70.52966640000001</v>
       </c>
       <c r="N48">
-        <v>-41.72903520000001</v>
+        <v>-43.22966640000001</v>
       </c>
       <c r="O48">
-        <v>-4.172903520000001</v>
+        <v>-4.322966640000002</v>
       </c>
       <c r="P48">
-        <v>-37.55613168000001</v>
+        <v>-38.90669976000001</v>
       </c>
       <c r="Q48">
-        <v>-14.85613168000001</v>
+        <v>-16.20669976000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1421575277568065</v>
+        <v>0.1439755943182557</v>
       </c>
       <c r="T48">
-        <v>1.49062030903174</v>
+        <v>1.518745220522905</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03954857535079673</v>
+        <v>0.03870711630077978</v>
       </c>
       <c r="W48">
-        <v>0.2264744459322821</v>
+        <v>0.2266728619762761</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3954857535079672</v>
+        <v>0.3870711630077978</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1828433101175253</v>
+        <v>0.1847433101175253</v>
       </c>
       <c r="C49">
-        <v>-19.98199121540694</v>
+        <v>-29.74522131979774</v>
       </c>
       <c r="D49">
-        <v>258.6260087845931</v>
+        <v>255.2267786802024</v>
       </c>
       <c r="E49">
-        <v>244.9080000000001</v>
+        <v>251.2720000000001</v>
       </c>
       <c r="F49">
-        <v>299.1080000000001</v>
+        <v>305.4720000000001</v>
       </c>
       <c r="G49">
         <v>20.5</v>
@@ -5305,37 +5305,37 @@
         <v>27.3</v>
       </c>
       <c r="M49">
-        <v>70.52966640000001</v>
+        <v>72.03029760000003</v>
       </c>
       <c r="N49">
-        <v>-43.22966640000001</v>
+        <v>-44.73029760000003</v>
       </c>
       <c r="O49">
-        <v>-4.322966640000002</v>
+        <v>-4.473029760000003</v>
       </c>
       <c r="P49">
-        <v>-38.90669976000001</v>
+        <v>-40.25726784000003</v>
       </c>
       <c r="Q49">
-        <v>-16.20669976000001</v>
+        <v>-17.55726784000003</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1439755943182557</v>
+        <v>0.1458635865166837</v>
       </c>
       <c r="T49">
-        <v>1.518745220522905</v>
+        <v>1.547951859379114</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03870711630077978</v>
+        <v>0.03790071804451352</v>
       </c>
       <c r="W49">
-        <v>0.2266728619762761</v>
+        <v>0.2268630106851037</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3870711630077978</v>
+        <v>0.3790071804451352</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1847433101175253</v>
+        <v>0.1866433101175253</v>
       </c>
       <c r="C50">
-        <v>-29.74522131979768</v>
+        <v>-39.42025560494915</v>
       </c>
       <c r="D50">
-        <v>255.2267786802024</v>
+        <v>251.9157443950509</v>
       </c>
       <c r="E50">
-        <v>251.272</v>
+        <v>257.636</v>
       </c>
       <c r="F50">
-        <v>305.472</v>
+        <v>311.836</v>
       </c>
       <c r="G50">
         <v>20.5</v>
@@ -5387,37 +5387,37 @@
         <v>27.3</v>
       </c>
       <c r="M50">
-        <v>72.03029760000001</v>
+        <v>73.53092880000001</v>
       </c>
       <c r="N50">
-        <v>-44.73029760000001</v>
+        <v>-46.23092880000002</v>
       </c>
       <c r="O50">
-        <v>-4.473029760000002</v>
+        <v>-4.623092880000002</v>
       </c>
       <c r="P50">
-        <v>-40.25726784000001</v>
+        <v>-41.60783592000001</v>
       </c>
       <c r="Q50">
-        <v>-17.55726784000001</v>
+        <v>-18.90783592000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1458635865166837</v>
+        <v>0.1478256176248539</v>
       </c>
       <c r="T50">
-        <v>1.547951859379114</v>
+        <v>1.578303856621842</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03790071804451353</v>
+        <v>0.03712723400278876</v>
       </c>
       <c r="W50">
-        <v>0.2268630106851037</v>
+        <v>0.2270453982221424</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3790071804451353</v>
+        <v>0.3712723400278876</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1866433101175253</v>
+        <v>0.1885433101175253</v>
       </c>
       <c r="C51">
-        <v>-39.42025560494915</v>
+        <v>-49.01048258155481</v>
       </c>
       <c r="D51">
-        <v>251.9157443950509</v>
+        <v>248.6895174184452</v>
       </c>
       <c r="E51">
-        <v>257.636</v>
+        <v>264.0000000000001</v>
       </c>
       <c r="F51">
-        <v>311.836</v>
+        <v>318.2</v>
       </c>
       <c r="G51">
         <v>20.5</v>
@@ -5469,37 +5469,37 @@
         <v>27.3</v>
       </c>
       <c r="M51">
-        <v>73.53092880000001</v>
+        <v>75.03156000000001</v>
       </c>
       <c r="N51">
-        <v>-46.23092880000002</v>
+        <v>-47.73156000000002</v>
       </c>
       <c r="O51">
-        <v>-4.623092880000002</v>
+        <v>-4.773156000000002</v>
       </c>
       <c r="P51">
-        <v>-41.60783592000001</v>
+        <v>-42.95840400000002</v>
       </c>
       <c r="Q51">
-        <v>-18.90783592000001</v>
+        <v>-20.25840400000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1478256176248539</v>
+        <v>0.149866129977351</v>
       </c>
       <c r="T51">
-        <v>1.578303856621842</v>
+        <v>1.609869933754279</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03712723400278876</v>
+        <v>0.03638468932273299</v>
       </c>
       <c r="W51">
-        <v>0.2270453982221424</v>
+        <v>0.2272204902576996</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3712723400278876</v>
+        <v>0.3638468932273299</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1885433101175253</v>
+        <v>0.1904433101175253</v>
       </c>
       <c r="C52">
-        <v>-49.01048258155481</v>
+        <v>-58.51911937173514</v>
       </c>
       <c r="D52">
-        <v>248.6895174184452</v>
+        <v>245.5448806282649</v>
       </c>
       <c r="E52">
-        <v>264.0000000000001</v>
+        <v>270.3640000000001</v>
       </c>
       <c r="F52">
-        <v>318.2</v>
+        <v>324.5640000000001</v>
       </c>
       <c r="G52">
         <v>20.5</v>
@@ -5551,37 +5551,37 @@
         <v>27.3</v>
       </c>
       <c r="M52">
-        <v>75.03156000000001</v>
+        <v>76.53219120000003</v>
       </c>
       <c r="N52">
-        <v>-47.73156000000002</v>
+        <v>-49.23219120000003</v>
       </c>
       <c r="O52">
-        <v>-4.773156000000002</v>
+        <v>-4.923219120000003</v>
       </c>
       <c r="P52">
-        <v>-42.95840400000002</v>
+        <v>-44.30897208000003</v>
       </c>
       <c r="Q52">
-        <v>-20.25840400000002</v>
+        <v>-21.60897208000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.149866129977351</v>
+        <v>0.1519899285483174</v>
       </c>
       <c r="T52">
-        <v>1.609869933754279</v>
+        <v>1.642724422198244</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03638468932273299</v>
+        <v>0.03567126404189508</v>
       </c>
       <c r="W52">
-        <v>0.2272204902576996</v>
+        <v>0.2273887159389212</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3638468932273299</v>
+        <v>0.3567126404189508</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1904433101175253</v>
+        <v>0.1923433101175253</v>
       </c>
       <c r="C53">
-        <v>-58.51911937173514</v>
+        <v>-67.94922240962723</v>
       </c>
       <c r="D53">
-        <v>245.5448806282649</v>
+        <v>242.4787775903728</v>
       </c>
       <c r="E53">
-        <v>270.3640000000001</v>
+        <v>276.7280000000001</v>
       </c>
       <c r="F53">
-        <v>324.5640000000001</v>
+        <v>330.9280000000001</v>
       </c>
       <c r="G53">
         <v>20.5</v>
@@ -5633,37 +5633,37 @@
         <v>27.3</v>
       </c>
       <c r="M53">
-        <v>76.53219120000003</v>
+        <v>78.03282240000001</v>
       </c>
       <c r="N53">
-        <v>-49.23219120000003</v>
+        <v>-50.73282240000002</v>
       </c>
       <c r="O53">
-        <v>-4.923219120000003</v>
+        <v>-5.073282240000002</v>
       </c>
       <c r="P53">
-        <v>-44.30897208000003</v>
+        <v>-45.65954016000001</v>
       </c>
       <c r="Q53">
-        <v>-21.60897208000003</v>
+        <v>-22.95954016000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1519899285483174</v>
+        <v>0.1542022187264073</v>
       </c>
       <c r="T53">
-        <v>1.642724422198244</v>
+        <v>1.676947847660707</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03567126404189508</v>
+        <v>0.03498527819493557</v>
       </c>
       <c r="W53">
-        <v>0.2273887159389212</v>
+        <v>0.2275504714016342</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3567126404189508</v>
+        <v>0.3498527819493557</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1923433101175253</v>
+        <v>0.1942433101175253</v>
       </c>
       <c r="C54">
-        <v>-67.94922240962723</v>
+        <v>-77.30369735015762</v>
       </c>
       <c r="D54">
-        <v>242.4787775903728</v>
+        <v>239.4883026498425</v>
       </c>
       <c r="E54">
-        <v>276.7280000000001</v>
+        <v>283.0920000000001</v>
       </c>
       <c r="F54">
-        <v>330.9280000000001</v>
+        <v>337.2920000000001</v>
       </c>
       <c r="G54">
         <v>20.5</v>
@@ -5715,37 +5715,37 @@
         <v>27.3</v>
       </c>
       <c r="M54">
-        <v>78.03282240000001</v>
+        <v>79.53345360000003</v>
       </c>
       <c r="N54">
-        <v>-50.73282240000002</v>
+        <v>-52.23345360000003</v>
       </c>
       <c r="O54">
-        <v>-5.073282240000002</v>
+        <v>-5.223345360000003</v>
       </c>
       <c r="P54">
-        <v>-45.65954016000001</v>
+        <v>-47.01010824000003</v>
       </c>
       <c r="Q54">
-        <v>-22.95954016000001</v>
+        <v>-24.31010824000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1542022187264073</v>
+        <v>0.1565086489120756</v>
       </c>
       <c r="T54">
-        <v>1.676947847660707</v>
+        <v>1.712627589100297</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03498527819493557</v>
+        <v>0.03432517860635187</v>
       </c>
       <c r="W54">
-        <v>0.2275504714016342</v>
+        <v>0.2277061228846222</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3498527819493557</v>
+        <v>0.3432517860635187</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1942433101175253</v>
+        <v>0.1961433101175253</v>
       </c>
       <c r="C55">
-        <v>-77.30369735015762</v>
+        <v>-86.58530825352028</v>
       </c>
       <c r="D55">
-        <v>239.4883026498425</v>
+        <v>236.5706917464798</v>
       </c>
       <c r="E55">
-        <v>283.0920000000001</v>
+        <v>289.4560000000001</v>
       </c>
       <c r="F55">
-        <v>337.2920000000001</v>
+        <v>343.6560000000001</v>
       </c>
       <c r="G55">
         <v>20.5</v>
@@ -5797,37 +5797,37 @@
         <v>27.3</v>
       </c>
       <c r="M55">
-        <v>79.53345360000003</v>
+        <v>81.03408480000002</v>
       </c>
       <c r="N55">
-        <v>-52.23345360000003</v>
+        <v>-53.73408480000002</v>
       </c>
       <c r="O55">
-        <v>-5.223345360000003</v>
+        <v>-5.373408480000002</v>
       </c>
       <c r="P55">
-        <v>-47.01010824000003</v>
+        <v>-48.36067632000002</v>
       </c>
       <c r="Q55">
-        <v>-24.31010824000003</v>
+        <v>-25.66067632000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1565086489120756</v>
+        <v>0.1589153586710337</v>
       </c>
       <c r="T55">
-        <v>1.712627589100297</v>
+        <v>1.749858623645956</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03432517860635187</v>
+        <v>0.0336895271506787</v>
       </c>
       <c r="W55">
-        <v>0.2277061228846222</v>
+        <v>0.22785600949787</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3432517860635187</v>
+        <v>0.3368952715067869</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1961433101175253</v>
+        <v>0.1980433101175253</v>
       </c>
       <c r="C56">
-        <v>-86.58530825352028</v>
+        <v>-95.79668610638828</v>
       </c>
       <c r="D56">
-        <v>236.5706917464798</v>
+        <v>233.7233138936118</v>
       </c>
       <c r="E56">
-        <v>289.4560000000001</v>
+        <v>295.8200000000001</v>
       </c>
       <c r="F56">
-        <v>343.6560000000001</v>
+        <v>350.0200000000001</v>
       </c>
       <c r="G56">
         <v>20.5</v>
@@ -5879,37 +5879,37 @@
         <v>27.3</v>
       </c>
       <c r="M56">
-        <v>81.03408480000002</v>
+        <v>82.53471600000003</v>
       </c>
       <c r="N56">
-        <v>-53.73408480000002</v>
+        <v>-55.23471600000003</v>
       </c>
       <c r="O56">
-        <v>-5.373408480000002</v>
+        <v>-5.523471600000004</v>
       </c>
       <c r="P56">
-        <v>-48.36067632000002</v>
+        <v>-49.71124440000003</v>
       </c>
       <c r="Q56">
-        <v>-25.66067632000002</v>
+        <v>-27.01124440000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1589153586710337</v>
+        <v>0.1614290333081678</v>
       </c>
       <c r="T56">
-        <v>1.749858623645956</v>
+        <v>1.788744370838088</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0336895271506787</v>
+        <v>0.03307699029339362</v>
       </c>
       <c r="W56">
-        <v>0.22785600949787</v>
+        <v>0.2280004456888178</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3368952715067869</v>
+        <v>0.3307699029339362</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1980433101175253</v>
+        <v>0.1999433101175253</v>
       </c>
       <c r="C57">
-        <v>-95.79668610638828</v>
+        <v>-104.9403367350698</v>
       </c>
       <c r="D57">
-        <v>233.7233138936118</v>
+        <v>230.9436632649303</v>
       </c>
       <c r="E57">
-        <v>295.8200000000001</v>
+        <v>302.1840000000001</v>
       </c>
       <c r="F57">
-        <v>350.0200000000001</v>
+        <v>356.3840000000001</v>
       </c>
       <c r="G57">
         <v>20.5</v>
@@ -5961,37 +5961,37 @@
         <v>27.3</v>
       </c>
       <c r="M57">
-        <v>82.53471600000003</v>
+        <v>84.03534720000002</v>
       </c>
       <c r="N57">
-        <v>-55.23471600000003</v>
+        <v>-56.73534720000002</v>
       </c>
       <c r="O57">
-        <v>-5.523471600000004</v>
+        <v>-5.673534720000003</v>
       </c>
       <c r="P57">
-        <v>-49.71124440000003</v>
+        <v>-51.06181248000001</v>
       </c>
       <c r="Q57">
-        <v>-27.01124440000003</v>
+        <v>-28.36181248000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1614290333081678</v>
+        <v>0.1640569658833534</v>
       </c>
       <c r="T57">
-        <v>1.788744370838088</v>
+        <v>1.829397651993499</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03307699029339362</v>
+        <v>0.03248632975244017</v>
       </c>
       <c r="W57">
-        <v>0.2280004456888178</v>
+        <v>0.2281397234443746</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3307699029339362</v>
+        <v>0.3248632975244016</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1999433101175253</v>
+        <v>0.2018433101175253</v>
       </c>
       <c r="C58">
-        <v>-104.9403367350698</v>
+        <v>-114.0186481606414</v>
       </c>
       <c r="D58">
-        <v>230.9436632649303</v>
+        <v>228.2293518393587</v>
       </c>
       <c r="E58">
-        <v>302.1840000000001</v>
+        <v>308.5480000000001</v>
       </c>
       <c r="F58">
-        <v>356.3840000000001</v>
+        <v>362.7480000000001</v>
       </c>
       <c r="G58">
         <v>20.5</v>
@@ -6043,37 +6043,37 @@
         <v>27.3</v>
       </c>
       <c r="M58">
-        <v>84.03534720000002</v>
+        <v>85.53597840000003</v>
       </c>
       <c r="N58">
-        <v>-56.73534720000002</v>
+        <v>-58.23597840000004</v>
       </c>
       <c r="O58">
-        <v>-5.673534720000003</v>
+        <v>-5.823597840000004</v>
       </c>
       <c r="P58">
-        <v>-51.06181248000001</v>
+        <v>-52.41238056000003</v>
       </c>
       <c r="Q58">
-        <v>-28.36181248000002</v>
+        <v>-29.71238056000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1640569658833534</v>
+        <v>0.1668071278806408</v>
       </c>
       <c r="T58">
-        <v>1.829397651993499</v>
+        <v>1.871941783435209</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03248632975244017</v>
+        <v>0.03191639414274823</v>
       </c>
       <c r="W58">
-        <v>0.2281397234443746</v>
+        <v>0.22827411426114</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3248632975244016</v>
+        <v>0.3191639414274823</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2018433101175253</v>
+        <v>0.2037433101175253</v>
       </c>
       <c r="C59">
-        <v>-114.0186481606414</v>
+        <v>-123.0338974414284</v>
       </c>
       <c r="D59">
-        <v>228.2293518393587</v>
+        <v>225.5781025585717</v>
       </c>
       <c r="E59">
-        <v>308.5480000000001</v>
+        <v>314.9120000000001</v>
       </c>
       <c r="F59">
-        <v>362.7480000000001</v>
+        <v>369.1120000000001</v>
       </c>
       <c r="G59">
         <v>20.5</v>
@@ -6125,37 +6125,37 @@
         <v>27.3</v>
       </c>
       <c r="M59">
-        <v>85.53597840000003</v>
+        <v>87.03660960000002</v>
       </c>
       <c r="N59">
-        <v>-58.23597840000004</v>
+        <v>-59.73660960000002</v>
       </c>
       <c r="O59">
-        <v>-5.823597840000004</v>
+        <v>-5.973660960000003</v>
       </c>
       <c r="P59">
-        <v>-52.41238056000003</v>
+        <v>-53.76294864000002</v>
       </c>
       <c r="Q59">
-        <v>-29.71238056000003</v>
+        <v>-31.06294864000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1668071278806408</v>
+        <v>0.1696882499730369</v>
       </c>
       <c r="T59">
-        <v>1.871941783435209</v>
+        <v>1.916511825897951</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03191639414274823</v>
+        <v>0.03136611148511464</v>
       </c>
       <c r="W59">
-        <v>0.22827411426114</v>
+        <v>0.22840387091181</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3191639414274823</v>
+        <v>0.3136611148511464</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2037433101175253</v>
+        <v>0.2056433101175253</v>
       </c>
       <c r="C60">
-        <v>-123.0338974414283</v>
+        <v>-131.9882570440461</v>
       </c>
       <c r="D60">
-        <v>225.5781025585717</v>
+        <v>222.987742955954</v>
       </c>
       <c r="E60">
-        <v>314.912</v>
+        <v>321.2760000000001</v>
       </c>
       <c r="F60">
-        <v>369.112</v>
+        <v>375.4760000000001</v>
       </c>
       <c r="G60">
         <v>20.5</v>
@@ -6207,37 +6207,37 @@
         <v>27.3</v>
       </c>
       <c r="M60">
-        <v>87.03660960000001</v>
+        <v>88.53724080000002</v>
       </c>
       <c r="N60">
-        <v>-59.73660960000001</v>
+        <v>-61.23724080000002</v>
       </c>
       <c r="O60">
-        <v>-5.973660960000001</v>
+        <v>-6.123724080000002</v>
       </c>
       <c r="P60">
-        <v>-53.76294864</v>
+        <v>-55.11351672000002</v>
       </c>
       <c r="Q60">
-        <v>-31.06294864000001</v>
+        <v>-32.41351672000002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1696882499730369</v>
+        <v>0.1727099146065256</v>
       </c>
       <c r="T60">
-        <v>1.916511825897951</v>
+        <v>1.96325601677351</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03136611148511465</v>
+        <v>0.03083448247689236</v>
       </c>
       <c r="W60">
-        <v>0.22840387091181</v>
+        <v>0.2285292290319488</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3136611148511464</v>
+        <v>0.3083448247689236</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2056433101175253</v>
+        <v>0.2075433101175253</v>
       </c>
       <c r="C61">
-        <v>-131.9882570440461</v>
+        <v>-140.8838007804628</v>
       </c>
       <c r="D61">
-        <v>222.987742955954</v>
+        <v>220.4561992195372</v>
       </c>
       <c r="E61">
-        <v>321.2760000000001</v>
+        <v>327.64</v>
       </c>
       <c r="F61">
-        <v>375.4760000000001</v>
+        <v>381.84</v>
       </c>
       <c r="G61">
         <v>20.5</v>
@@ -6289,37 +6289,37 @@
         <v>27.3</v>
       </c>
       <c r="M61">
-        <v>88.53724080000002</v>
+        <v>90.03787200000001</v>
       </c>
       <c r="N61">
-        <v>-61.23724080000002</v>
+        <v>-62.73787200000001</v>
       </c>
       <c r="O61">
-        <v>-6.123724080000002</v>
+        <v>-6.273787200000001</v>
       </c>
       <c r="P61">
-        <v>-55.11351672000002</v>
+        <v>-56.46408480000001</v>
       </c>
       <c r="Q61">
-        <v>-32.41351672000002</v>
+        <v>-33.76408480000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1727099146065256</v>
+        <v>0.1758826624716887</v>
       </c>
       <c r="T61">
-        <v>1.96325601677351</v>
+        <v>2.012337417192848</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03083448247689236</v>
+        <v>0.03032057443561083</v>
       </c>
       <c r="W61">
-        <v>0.2285292290319488</v>
+        <v>0.228650408548083</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3083448247689236</v>
+        <v>0.3032057443561083</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2075433101175253</v>
+        <v>0.2094433101175253</v>
       </c>
       <c r="C62">
-        <v>-140.8838007804628</v>
+        <v>-149.7225093451887</v>
       </c>
       <c r="D62">
-        <v>220.4561992195372</v>
+        <v>217.9814906548114</v>
       </c>
       <c r="E62">
-        <v>327.64</v>
+        <v>334.0040000000001</v>
       </c>
       <c r="F62">
-        <v>381.84</v>
+        <v>388.2040000000001</v>
       </c>
       <c r="G62">
         <v>20.5</v>
@@ -6371,37 +6371,37 @@
         <v>27.3</v>
       </c>
       <c r="M62">
-        <v>90.03787200000001</v>
+        <v>91.53850320000002</v>
       </c>
       <c r="N62">
-        <v>-62.73787200000001</v>
+        <v>-64.23850320000003</v>
       </c>
       <c r="O62">
-        <v>-6.273787200000001</v>
+        <v>-6.423850320000003</v>
       </c>
       <c r="P62">
-        <v>-56.46408480000001</v>
+        <v>-57.81465288000003</v>
       </c>
       <c r="Q62">
-        <v>-33.76408480000001</v>
+        <v>-35.11465288000002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1758826624716887</v>
+        <v>0.1792181153555782</v>
       </c>
       <c r="T62">
-        <v>2.012337417192848</v>
+        <v>2.063935812505486</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03032057443561083</v>
+        <v>0.02982351583830573</v>
       </c>
       <c r="W62">
-        <v>0.228650408548083</v>
+        <v>0.2287676149653275</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3032057443561083</v>
+        <v>0.2982351583830573</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2094433101175253</v>
+        <v>0.2113433101175253</v>
       </c>
       <c r="C63">
-        <v>-149.7225093451887</v>
+        <v>-158.5062754836606</v>
       </c>
       <c r="D63">
-        <v>217.9814906548114</v>
+        <v>215.5617245163394</v>
       </c>
       <c r="E63">
-        <v>334.0040000000001</v>
+        <v>340.3680000000001</v>
       </c>
       <c r="F63">
-        <v>388.2040000000001</v>
+        <v>394.568</v>
       </c>
       <c r="G63">
         <v>20.5</v>
@@ -6453,37 +6453,37 @@
         <v>27.3</v>
       </c>
       <c r="M63">
-        <v>91.53850320000002</v>
+        <v>93.03913440000001</v>
       </c>
       <c r="N63">
-        <v>-64.23850320000003</v>
+        <v>-65.73913440000001</v>
       </c>
       <c r="O63">
-        <v>-6.423850320000003</v>
+        <v>-6.573913440000002</v>
       </c>
       <c r="P63">
-        <v>-57.81465288000003</v>
+        <v>-59.16522096000001</v>
       </c>
       <c r="Q63">
-        <v>-35.11465288000002</v>
+        <v>-36.46522096000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1792181153555782</v>
+        <v>0.1827291183912514</v>
       </c>
       <c r="T63">
-        <v>2.063935812505486</v>
+        <v>2.118249912834578</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02982351583830573</v>
+        <v>0.0293424913893008</v>
       </c>
       <c r="W63">
-        <v>0.2287676149653275</v>
+        <v>0.2288810405304029</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2982351583830573</v>
+        <v>0.293424913893008</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2113433101175253</v>
+        <v>0.2132433101175253</v>
       </c>
       <c r="C64">
-        <v>-158.5062754836606</v>
+        <v>-167.2369088201687</v>
       </c>
       <c r="D64">
-        <v>215.5617245163394</v>
+        <v>213.1950911798314</v>
       </c>
       <c r="E64">
-        <v>340.3680000000001</v>
+        <v>346.7320000000001</v>
       </c>
       <c r="F64">
-        <v>394.568</v>
+        <v>400.9320000000001</v>
       </c>
       <c r="G64">
         <v>20.5</v>
@@ -6535,37 +6535,37 @@
         <v>27.3</v>
       </c>
       <c r="M64">
-        <v>93.03913440000001</v>
+        <v>94.53976560000002</v>
       </c>
       <c r="N64">
-        <v>-65.73913440000001</v>
+        <v>-67.23976560000003</v>
       </c>
       <c r="O64">
-        <v>-6.573913440000002</v>
+        <v>-6.723976560000003</v>
       </c>
       <c r="P64">
-        <v>-59.16522096000001</v>
+        <v>-60.51578904000002</v>
       </c>
       <c r="Q64">
-        <v>-36.46522096000001</v>
+        <v>-37.81578904000003</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1827291183912514</v>
+        <v>0.1864299053747987</v>
       </c>
       <c r="T64">
-        <v>2.118249912834578</v>
+        <v>2.175499910478755</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0293424913893008</v>
+        <v>0.02887673755772459</v>
       </c>
       <c r="W64">
-        <v>0.2288810405304029</v>
+        <v>0.2289908652838886</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.293424913893008</v>
+        <v>0.2887673755772459</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2132433101175253</v>
+        <v>0.2151433101175253</v>
       </c>
       <c r="C65">
-        <v>-167.2369088201687</v>
+        <v>-175.9161403712031</v>
       </c>
       <c r="D65">
-        <v>213.1950911798314</v>
+        <v>210.8798596287969</v>
       </c>
       <c r="E65">
-        <v>346.7320000000001</v>
+        <v>353.0960000000001</v>
       </c>
       <c r="F65">
-        <v>400.9320000000001</v>
+        <v>407.296</v>
       </c>
       <c r="G65">
         <v>20.5</v>
@@ -6617,37 +6617,37 @@
         <v>27.3</v>
       </c>
       <c r="M65">
-        <v>94.53976560000002</v>
+        <v>96.04039680000001</v>
       </c>
       <c r="N65">
-        <v>-67.23976560000003</v>
+        <v>-68.74039680000001</v>
       </c>
       <c r="O65">
-        <v>-6.723976560000003</v>
+        <v>-6.874039680000002</v>
       </c>
       <c r="P65">
-        <v>-60.51578904000002</v>
+        <v>-61.86635712000001</v>
       </c>
       <c r="Q65">
-        <v>-37.81578904000003</v>
+        <v>-39.16635712000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1864299053747987</v>
+        <v>0.1903362916352098</v>
       </c>
       <c r="T65">
-        <v>2.175499910478755</v>
+        <v>2.23593046354761</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02887673755772459</v>
+        <v>0.02842553853338515</v>
       </c>
       <c r="W65">
-        <v>0.2289908652838886</v>
+        <v>0.2290972580138278</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2887673755772459</v>
+        <v>0.2842553853338514</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2151433101175253</v>
+        <v>0.2170433101175253</v>
       </c>
       <c r="C66">
-        <v>-175.9161403712031</v>
+        <v>-184.5456267678805</v>
       </c>
       <c r="D66">
-        <v>210.8798596287969</v>
+        <v>208.6143732321196</v>
       </c>
       <c r="E66">
-        <v>353.0960000000001</v>
+        <v>359.4600000000001</v>
       </c>
       <c r="F66">
-        <v>407.296</v>
+        <v>413.6600000000001</v>
       </c>
       <c r="G66">
         <v>20.5</v>
@@ -6699,37 +6699,37 @@
         <v>27.3</v>
       </c>
       <c r="M66">
-        <v>96.04039680000001</v>
+        <v>97.54102800000003</v>
       </c>
       <c r="N66">
-        <v>-68.74039680000001</v>
+        <v>-70.24102800000003</v>
       </c>
       <c r="O66">
-        <v>-6.874039680000002</v>
+        <v>-7.024102800000003</v>
       </c>
       <c r="P66">
-        <v>-61.86635712000001</v>
+        <v>-63.21692520000003</v>
       </c>
       <c r="Q66">
-        <v>-39.16635712000001</v>
+        <v>-40.51692520000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1903362916352098</v>
+        <v>0.1944658999676444</v>
       </c>
       <c r="T66">
-        <v>2.23593046354761</v>
+        <v>2.299814191077542</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02842553853338515</v>
+        <v>0.02798822255594845</v>
       </c>
       <c r="W66">
-        <v>0.2290972580138278</v>
+        <v>0.2292003771213074</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2842553853338514</v>
+        <v>0.2798822255594845</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2170433101175253</v>
+        <v>0.2189433101175253</v>
       </c>
       <c r="C67">
-        <v>-184.5456267678805</v>
+        <v>-193.1269542090917</v>
       </c>
       <c r="D67">
-        <v>208.6143732321196</v>
+        <v>206.3970457909083</v>
       </c>
       <c r="E67">
-        <v>359.4600000000001</v>
+        <v>365.8240000000001</v>
       </c>
       <c r="F67">
-        <v>413.6600000000001</v>
+        <v>420.0240000000001</v>
       </c>
       <c r="G67">
         <v>20.5</v>
@@ -6781,37 +6781,37 @@
         <v>27.3</v>
       </c>
       <c r="M67">
-        <v>97.54102800000003</v>
+        <v>99.04165920000001</v>
       </c>
       <c r="N67">
-        <v>-70.24102800000003</v>
+        <v>-71.74165920000002</v>
       </c>
       <c r="O67">
-        <v>-7.024102800000003</v>
+        <v>-7.174165920000002</v>
       </c>
       <c r="P67">
-        <v>-63.21692520000003</v>
+        <v>-64.56749328000001</v>
       </c>
       <c r="Q67">
-        <v>-40.51692520000003</v>
+        <v>-41.86749328000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1944658999676444</v>
+        <v>0.1988384264372809</v>
       </c>
       <c r="T67">
-        <v>2.299814191077542</v>
+        <v>2.367455784932763</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02798822255594845</v>
+        <v>0.02756415857782803</v>
       </c>
       <c r="W67">
-        <v>0.2292003771213074</v>
+        <v>0.2293003714073482</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2798822255594845</v>
+        <v>0.2756415857782802</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2189433101175253</v>
+        <v>0.2208433101175253</v>
       </c>
       <c r="C68">
-        <v>-193.1269542090917</v>
+        <v>-201.6616421651985</v>
       </c>
       <c r="D68">
-        <v>206.3970457909083</v>
+        <v>204.2263578348015</v>
       </c>
       <c r="E68">
-        <v>365.8240000000001</v>
+        <v>372.1880000000001</v>
       </c>
       <c r="F68">
-        <v>420.0240000000001</v>
+        <v>426.3880000000001</v>
       </c>
       <c r="G68">
         <v>20.5</v>
@@ -6863,37 +6863,37 @@
         <v>27.3</v>
       </c>
       <c r="M68">
-        <v>99.04165920000001</v>
+        <v>100.5422904</v>
       </c>
       <c r="N68">
-        <v>-71.74165920000002</v>
+        <v>-73.24229040000003</v>
       </c>
       <c r="O68">
-        <v>-7.174165920000002</v>
+        <v>-7.324229040000003</v>
       </c>
       <c r="P68">
-        <v>-64.56749328000001</v>
+        <v>-65.91806136000002</v>
       </c>
       <c r="Q68">
-        <v>-41.86749328000001</v>
+        <v>-43.21806136000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1988384264372809</v>
+        <v>0.2034759545111379</v>
       </c>
       <c r="T68">
-        <v>2.367455784932763</v>
+        <v>2.439196869324666</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02756415857782803</v>
+        <v>0.02715275322592014</v>
       </c>
       <c r="W68">
-        <v>0.2293003714073482</v>
+        <v>0.229397380789328</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2756415857782802</v>
+        <v>0.2715275322592013</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2208433101175253</v>
+        <v>0.2227433101175253</v>
       </c>
       <c r="C69">
-        <v>-201.6616421651985</v>
+        <v>-210.1511468504499</v>
       </c>
       <c r="D69">
-        <v>204.2263578348015</v>
+        <v>202.1008531495502</v>
       </c>
       <c r="E69">
-        <v>372.1880000000001</v>
+        <v>378.5520000000001</v>
       </c>
       <c r="F69">
-        <v>426.3880000000001</v>
+        <v>432.7520000000001</v>
       </c>
       <c r="G69">
         <v>20.5</v>
@@ -6945,37 +6945,37 @@
         <v>27.3</v>
       </c>
       <c r="M69">
-        <v>100.5422904</v>
+        <v>102.0429216</v>
       </c>
       <c r="N69">
-        <v>-73.24229040000003</v>
+        <v>-74.74292160000002</v>
       </c>
       <c r="O69">
-        <v>-7.324229040000003</v>
+        <v>-7.474292160000002</v>
       </c>
       <c r="P69">
-        <v>-65.91806136000002</v>
+        <v>-67.26862944000001</v>
       </c>
       <c r="Q69">
-        <v>-43.21806136000002</v>
+        <v>-44.56862944000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2034759545111379</v>
+        <v>0.208403328089611</v>
       </c>
       <c r="T69">
-        <v>2.439196869324666</v>
+        <v>2.515421771491061</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02715275322592014</v>
+        <v>0.02675344803142132</v>
       </c>
       <c r="W69">
-        <v>0.229397380789328</v>
+        <v>0.2294915369541909</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2715275322592013</v>
+        <v>0.2675344803142131</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2227433101175253</v>
+        <v>0.2246433101175253</v>
       </c>
       <c r="C70">
-        <v>-210.1511468504499</v>
+        <v>-218.5968644807957</v>
       </c>
       <c r="D70">
-        <v>202.1008531495502</v>
+        <v>200.0191355192044</v>
       </c>
       <c r="E70">
-        <v>378.5520000000001</v>
+        <v>384.9160000000001</v>
       </c>
       <c r="F70">
-        <v>432.7520000000001</v>
+        <v>439.1160000000001</v>
       </c>
       <c r="G70">
         <v>20.5</v>
@@ -7027,37 +7027,37 @@
         <v>27.3</v>
       </c>
       <c r="M70">
-        <v>102.0429216</v>
+        <v>103.5435528</v>
       </c>
       <c r="N70">
-        <v>-74.74292160000002</v>
+        <v>-76.24355280000003</v>
       </c>
       <c r="O70">
-        <v>-7.474292160000002</v>
+        <v>-7.624355280000003</v>
       </c>
       <c r="P70">
-        <v>-67.26862944000001</v>
+        <v>-68.61919752000003</v>
       </c>
       <c r="Q70">
-        <v>-44.56862944000001</v>
+        <v>-45.91919752000003</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.208403328089611</v>
+        <v>0.213648596737663</v>
       </c>
       <c r="T70">
-        <v>2.515421771491061</v>
+        <v>2.596564409281096</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02675344803142132</v>
+        <v>0.02636571690053115</v>
       </c>
       <c r="W70">
-        <v>0.2294915369541909</v>
+        <v>0.2295829639548548</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2675344803142131</v>
+        <v>0.2636571690053114</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2246433101175253</v>
+        <v>0.2265433101175253</v>
       </c>
       <c r="C71">
-        <v>-218.5968644807957</v>
+        <v>-227.0001343324116</v>
       </c>
       <c r="D71">
-        <v>200.0191355192044</v>
+        <v>197.9798656675886</v>
       </c>
       <c r="E71">
-        <v>384.9160000000001</v>
+        <v>391.2800000000001</v>
       </c>
       <c r="F71">
-        <v>439.1160000000001</v>
+        <v>445.4800000000001</v>
       </c>
       <c r="G71">
         <v>20.5</v>
@@ -7109,37 +7109,37 @@
         <v>27.3</v>
       </c>
       <c r="M71">
-        <v>103.5435528</v>
+        <v>105.044184</v>
       </c>
       <c r="N71">
-        <v>-76.24355280000003</v>
+        <v>-77.74418400000003</v>
       </c>
       <c r="O71">
-        <v>-7.624355280000003</v>
+        <v>-7.774418400000004</v>
       </c>
       <c r="P71">
-        <v>-68.61919752000003</v>
+        <v>-69.96976560000003</v>
       </c>
       <c r="Q71">
-        <v>-45.91919752000003</v>
+        <v>-47.26976560000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.213648596737663</v>
+        <v>0.2192435499622517</v>
       </c>
       <c r="T71">
-        <v>2.596564409281096</v>
+        <v>2.683116556257132</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02636571690053115</v>
+        <v>0.02598906380195214</v>
       </c>
       <c r="W71">
-        <v>0.2295829639548548</v>
+        <v>0.2296717787554997</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2636571690053114</v>
+        <v>0.2598906380195213</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2265433101175253</v>
+        <v>0.2284433101175253</v>
       </c>
       <c r="C72">
-        <v>-227.0001343324116</v>
+        <v>-235.3622416150158</v>
       </c>
       <c r="D72">
-        <v>197.9798656675886</v>
+        <v>195.9817583849843</v>
       </c>
       <c r="E72">
-        <v>391.2800000000001</v>
+        <v>397.6440000000001</v>
       </c>
       <c r="F72">
-        <v>445.4800000000001</v>
+        <v>451.8440000000001</v>
       </c>
       <c r="G72">
         <v>20.5</v>
@@ -7191,37 +7191,37 @@
         <v>27.3</v>
       </c>
       <c r="M72">
-        <v>105.044184</v>
+        <v>106.5448152</v>
       </c>
       <c r="N72">
-        <v>-77.74418400000003</v>
+        <v>-79.24481520000003</v>
       </c>
       <c r="O72">
-        <v>-7.774418400000004</v>
+        <v>-7.924481520000004</v>
       </c>
       <c r="P72">
-        <v>-69.96976560000003</v>
+        <v>-71.32033368000003</v>
       </c>
       <c r="Q72">
-        <v>-47.26976560000003</v>
+        <v>-48.62033368000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2192435499622517</v>
+        <v>0.2252243620299156</v>
       </c>
       <c r="T72">
-        <v>2.683116556257132</v>
+        <v>2.775637816817723</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02598906380195214</v>
+        <v>0.02562302064981196</v>
       </c>
       <c r="W72">
-        <v>0.2296717787554997</v>
+        <v>0.2297580917307744</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2598906380195213</v>
+        <v>0.2562302064981196</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2284433101175253</v>
+        <v>0.2303433101175253</v>
       </c>
       <c r="C73">
-        <v>-235.3622416150158</v>
+        <v>-243.6844201729321</v>
       </c>
       <c r="D73">
-        <v>195.9817583849843</v>
+        <v>194.023579827068</v>
       </c>
       <c r="E73">
-        <v>397.6440000000001</v>
+        <v>404.008</v>
       </c>
       <c r="F73">
-        <v>451.8440000000001</v>
+        <v>458.208</v>
       </c>
       <c r="G73">
         <v>20.5</v>
@@ -7273,37 +7273,37 @@
         <v>27.3</v>
       </c>
       <c r="M73">
-        <v>106.5448152</v>
+        <v>108.0454464</v>
       </c>
       <c r="N73">
-        <v>-79.24481520000002</v>
+        <v>-80.74544640000002</v>
       </c>
       <c r="O73">
-        <v>-7.924481520000002</v>
+        <v>-8.074544640000003</v>
       </c>
       <c r="P73">
-        <v>-71.32033368000002</v>
+        <v>-72.67090176000002</v>
       </c>
       <c r="Q73">
-        <v>-48.62033368000002</v>
+        <v>-49.97090176000002</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2252243620299155</v>
+        <v>0.2316323749595554</v>
       </c>
       <c r="T73">
-        <v>2.775637816817722</v>
+        <v>2.874767738846927</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02562302064981196</v>
+        <v>0.02526714536300902</v>
       </c>
       <c r="W73">
-        <v>0.2297580917307744</v>
+        <v>0.2298420071234025</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2562302064981196</v>
+        <v>0.2526714536300901</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2303433101175253</v>
+        <v>0.2322433101175253</v>
       </c>
       <c r="C74">
-        <v>-243.6844201729321</v>
+        <v>-251.9678550258245</v>
       </c>
       <c r="D74">
-        <v>194.023579827068</v>
+        <v>192.1041449741756</v>
       </c>
       <c r="E74">
-        <v>404.008</v>
+        <v>410.3720000000001</v>
       </c>
       <c r="F74">
-        <v>458.208</v>
+        <v>464.5720000000001</v>
       </c>
       <c r="G74">
         <v>20.5</v>
@@ -7355,37 +7355,37 @@
         <v>27.3</v>
       </c>
       <c r="M74">
-        <v>108.0454464</v>
+        <v>109.5460776</v>
       </c>
       <c r="N74">
-        <v>-80.74544640000002</v>
+        <v>-82.24607760000002</v>
       </c>
       <c r="O74">
-        <v>-8.074544640000003</v>
+        <v>-8.224607760000003</v>
       </c>
       <c r="P74">
-        <v>-72.67090176000002</v>
+        <v>-74.02146984000002</v>
       </c>
       <c r="Q74">
-        <v>-49.97090176000002</v>
+        <v>-51.32146984000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2316323749595554</v>
+        <v>0.238515055513613</v>
       </c>
       <c r="T74">
-        <v>2.874767738846927</v>
+        <v>2.981240618063479</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02526714536300902</v>
+        <v>0.02492102008406369</v>
       </c>
       <c r="W74">
-        <v>0.2298420071234025</v>
+        <v>0.2299236234641778</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2526714536300901</v>
+        <v>0.2492102008406368</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2322433101175253</v>
+        <v>0.2341433101175253</v>
       </c>
       <c r="C75">
-        <v>-251.9678550258245</v>
+        <v>-260.213684760101</v>
       </c>
       <c r="D75">
-        <v>192.1041449741756</v>
+        <v>190.222315239899</v>
       </c>
       <c r="E75">
-        <v>410.3720000000001</v>
+        <v>416.736</v>
       </c>
       <c r="F75">
-        <v>464.5720000000001</v>
+        <v>470.936</v>
       </c>
       <c r="G75">
         <v>20.5</v>
@@ -7437,37 +7437,37 @@
         <v>27.3</v>
       </c>
       <c r="M75">
-        <v>109.5460776</v>
+        <v>111.0467088</v>
       </c>
       <c r="N75">
-        <v>-82.24607760000002</v>
+        <v>-83.74670880000002</v>
       </c>
       <c r="O75">
-        <v>-8.224607760000003</v>
+        <v>-8.374670880000002</v>
       </c>
       <c r="P75">
-        <v>-74.02146984000002</v>
+        <v>-75.37203792000003</v>
       </c>
       <c r="Q75">
-        <v>-51.32146984000002</v>
+        <v>-52.67203792000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.238515055513613</v>
+        <v>0.2459271730333673</v>
       </c>
       <c r="T75">
-        <v>2.981240618063479</v>
+        <v>3.095903718758228</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02492102008406369</v>
+        <v>0.02458424954238716</v>
       </c>
       <c r="W75">
-        <v>0.2299236234641778</v>
+        <v>0.2300030339579051</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2492102008406368</v>
+        <v>0.2458424954238715</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2341433101175253</v>
+        <v>0.2360433101175253</v>
       </c>
       <c r="C76">
-        <v>-260.213684760101</v>
+        <v>-268.423003781125</v>
       </c>
       <c r="D76">
-        <v>190.222315239899</v>
+        <v>188.3769962188751</v>
       </c>
       <c r="E76">
-        <v>416.736</v>
+        <v>423.1000000000001</v>
       </c>
       <c r="F76">
-        <v>470.936</v>
+        <v>477.3000000000001</v>
       </c>
       <c r="G76">
         <v>20.5</v>
@@ -7519,37 +7519,37 @@
         <v>27.3</v>
       </c>
       <c r="M76">
-        <v>111.0467088</v>
+        <v>112.54734</v>
       </c>
       <c r="N76">
-        <v>-83.74670880000002</v>
+        <v>-85.24734000000002</v>
       </c>
       <c r="O76">
-        <v>-8.374670880000002</v>
+        <v>-8.524734000000002</v>
       </c>
       <c r="P76">
-        <v>-75.37203792000003</v>
+        <v>-76.72260600000001</v>
       </c>
       <c r="Q76">
-        <v>-52.67203792000002</v>
+        <v>-54.02260600000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2459271730333673</v>
+        <v>0.253932259954702</v>
       </c>
       <c r="T76">
-        <v>3.095903718758228</v>
+        <v>3.219739867508558</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02458424954238716</v>
+        <v>0.02425645954848866</v>
       </c>
       <c r="W76">
-        <v>0.2300030339579051</v>
+        <v>0.2300803268384664</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2458424954238715</v>
+        <v>0.2425645954848865</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2360433101175253</v>
+        <v>0.2379433101175253</v>
       </c>
       <c r="C77">
-        <v>-268.423003781125</v>
+        <v>-276.5968644355953</v>
       </c>
       <c r="D77">
-        <v>188.3769962188751</v>
+        <v>186.5671355644048</v>
       </c>
       <c r="E77">
-        <v>423.1000000000001</v>
+        <v>429.4640000000001</v>
       </c>
       <c r="F77">
-        <v>477.3000000000001</v>
+        <v>483.6640000000001</v>
       </c>
       <c r="G77">
         <v>20.5</v>
@@ -7601,37 +7601,37 @@
         <v>27.3</v>
       </c>
       <c r="M77">
-        <v>112.54734</v>
+        <v>114.0479712</v>
       </c>
       <c r="N77">
-        <v>-85.24734000000002</v>
+        <v>-86.74797120000004</v>
       </c>
       <c r="O77">
-        <v>-8.524734000000002</v>
+        <v>-8.674797120000004</v>
       </c>
       <c r="P77">
-        <v>-76.72260600000001</v>
+        <v>-78.07317408000003</v>
       </c>
       <c r="Q77">
-        <v>-54.02260600000001</v>
+        <v>-55.37317408000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.253932259954702</v>
+        <v>0.2626044374528146</v>
       </c>
       <c r="T77">
-        <v>3.219739867508558</v>
+        <v>3.353895695321414</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02425645954848866</v>
+        <v>0.02393729560706118</v>
       </c>
       <c r="W77">
-        <v>0.2300803268384664</v>
+        <v>0.230155585695855</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2425645954848865</v>
+        <v>0.2393729560706117</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2379433101175253</v>
+        <v>0.2398433101175253</v>
       </c>
       <c r="C78">
-        <v>-276.5968644355953</v>
+        <v>-284.7362790127451</v>
       </c>
       <c r="D78">
-        <v>186.5671355644048</v>
+        <v>184.791720987255</v>
       </c>
       <c r="E78">
-        <v>429.4640000000001</v>
+        <v>435.8280000000001</v>
       </c>
       <c r="F78">
-        <v>483.6640000000001</v>
+        <v>490.0280000000001</v>
       </c>
       <c r="G78">
         <v>20.5</v>
@@ -7683,37 +7683,37 @@
         <v>27.3</v>
       </c>
       <c r="M78">
-        <v>114.0479712</v>
+        <v>115.5486024</v>
       </c>
       <c r="N78">
-        <v>-86.74797120000004</v>
+        <v>-88.24860240000002</v>
       </c>
       <c r="O78">
-        <v>-8.674797120000004</v>
+        <v>-8.824860240000003</v>
       </c>
       <c r="P78">
-        <v>-78.07317408000003</v>
+        <v>-79.42374216000002</v>
       </c>
       <c r="Q78">
-        <v>-55.37317408000003</v>
+        <v>-56.72374216000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2626044374528146</v>
+        <v>0.2720307173420675</v>
       </c>
       <c r="T78">
-        <v>3.353895695321414</v>
+        <v>3.499717247291911</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02393729560706118</v>
+        <v>0.0236264216381383</v>
       </c>
       <c r="W78">
-        <v>0.230155585695855</v>
+        <v>0.230228889777727</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2393729560706117</v>
+        <v>0.2362642163813831</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2398433101175253</v>
+        <v>0.2417433101175253</v>
       </c>
       <c r="C79">
-        <v>-284.7362790127451</v>
+        <v>-292.8422216323539</v>
       </c>
       <c r="D79">
-        <v>184.791720987255</v>
+        <v>183.0497783676462</v>
       </c>
       <c r="E79">
-        <v>435.8280000000001</v>
+        <v>442.1920000000001</v>
       </c>
       <c r="F79">
-        <v>490.0280000000001</v>
+        <v>496.3920000000001</v>
       </c>
       <c r="G79">
         <v>20.5</v>
@@ -7765,37 +7765,37 @@
         <v>27.3</v>
       </c>
       <c r="M79">
-        <v>115.5486024</v>
+        <v>117.0492336</v>
       </c>
       <c r="N79">
-        <v>-88.24860240000002</v>
+        <v>-89.74923360000004</v>
       </c>
       <c r="O79">
-        <v>-8.824860240000003</v>
+        <v>-8.974923360000004</v>
       </c>
       <c r="P79">
-        <v>-79.42374216000002</v>
+        <v>-80.77431024000003</v>
       </c>
       <c r="Q79">
-        <v>-56.72374216000001</v>
+        <v>-58.07431024000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2720307173420675</v>
+        <v>0.2823139317667068</v>
       </c>
       <c r="T79">
-        <v>3.499717247291911</v>
+        <v>3.658795303986998</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0236264216381383</v>
+        <v>0.02332351879662371</v>
       </c>
       <c r="W79">
-        <v>0.230228889777727</v>
+        <v>0.2303003142677561</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2362642163813831</v>
+        <v>0.233235187966237</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2417433101175253</v>
+        <v>0.2436433101175253</v>
       </c>
       <c r="C80">
-        <v>-292.8422216323539</v>
+        <v>-300.9156300269725</v>
       </c>
       <c r="D80">
-        <v>183.0497783676462</v>
+        <v>181.3403699730276</v>
       </c>
       <c r="E80">
-        <v>442.1920000000001</v>
+        <v>448.5560000000001</v>
       </c>
       <c r="F80">
-        <v>496.3920000000001</v>
+        <v>502.7560000000001</v>
       </c>
       <c r="G80">
         <v>20.5</v>
@@ -7847,37 +7847,37 @@
         <v>27.3</v>
       </c>
       <c r="M80">
-        <v>117.0492336</v>
+        <v>118.5498648</v>
       </c>
       <c r="N80">
-        <v>-89.74923360000004</v>
+        <v>-91.24986480000003</v>
       </c>
       <c r="O80">
-        <v>-8.974923360000004</v>
+        <v>-9.124986480000002</v>
       </c>
       <c r="P80">
-        <v>-80.77431024000003</v>
+        <v>-82.12487832000002</v>
       </c>
       <c r="Q80">
-        <v>-58.07431024000003</v>
+        <v>-59.42487832000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2823139317667068</v>
+        <v>0.2935764999460739</v>
       </c>
       <c r="T80">
-        <v>3.658795303986998</v>
+        <v>3.833023651795903</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02332351879662371</v>
+        <v>0.02302828438147658</v>
       </c>
       <c r="W80">
-        <v>0.2303003142677561</v>
+        <v>0.2303699305428479</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.233235187966237</v>
+        <v>0.2302828438147657</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2436433101175253</v>
+        <v>0.2455433101175253</v>
       </c>
       <c r="C81">
-        <v>-300.9156300269725</v>
+        <v>-308.9574072252128</v>
       </c>
       <c r="D81">
-        <v>181.3403699730276</v>
+        <v>179.6625927747874</v>
       </c>
       <c r="E81">
-        <v>448.5560000000001</v>
+        <v>454.9200000000001</v>
       </c>
       <c r="F81">
-        <v>502.7560000000001</v>
+        <v>509.1200000000001</v>
       </c>
       <c r="G81">
         <v>20.5</v>
@@ -7929,37 +7929,37 @@
         <v>27.3</v>
       </c>
       <c r="M81">
-        <v>118.5498648</v>
+        <v>120.050496</v>
       </c>
       <c r="N81">
-        <v>-91.24986480000003</v>
+        <v>-92.75049600000004</v>
       </c>
       <c r="O81">
-        <v>-9.124986480000002</v>
+        <v>-9.275049600000004</v>
       </c>
       <c r="P81">
-        <v>-82.12487832000002</v>
+        <v>-83.47544640000004</v>
       </c>
       <c r="Q81">
-        <v>-59.42487832000002</v>
+        <v>-60.77544640000004</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2935764999460739</v>
+        <v>0.3059653249433776</v>
       </c>
       <c r="T81">
-        <v>3.833023651795903</v>
+        <v>4.024674834385698</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02302828438147658</v>
+        <v>0.02274043082670811</v>
       </c>
       <c r="W81">
-        <v>0.2303699305428479</v>
+        <v>0.2304378064110622</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2302828438147657</v>
+        <v>0.2274043082670811</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2455433101175253</v>
+        <v>0.2474433101175253</v>
       </c>
       <c r="C82">
-        <v>-308.9574072252128</v>
+        <v>-316.9684231424496</v>
       </c>
       <c r="D82">
-        <v>179.6625927747874</v>
+        <v>178.0155768575505</v>
       </c>
       <c r="E82">
-        <v>454.9200000000001</v>
+        <v>461.2840000000002</v>
       </c>
       <c r="F82">
-        <v>509.1200000000001</v>
+        <v>515.4840000000002</v>
       </c>
       <c r="G82">
         <v>20.5</v>
@@ -8011,37 +8011,37 @@
         <v>27.3</v>
       </c>
       <c r="M82">
-        <v>120.050496</v>
+        <v>121.5511272</v>
       </c>
       <c r="N82">
-        <v>-92.75049600000004</v>
+        <v>-94.25112720000004</v>
       </c>
       <c r="O82">
-        <v>-9.275049600000004</v>
+        <v>-9.425112720000005</v>
       </c>
       <c r="P82">
-        <v>-83.47544640000004</v>
+        <v>-84.82601448000004</v>
       </c>
       <c r="Q82">
-        <v>-60.77544640000004</v>
+        <v>-62.12601448000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3059653249433776</v>
+        <v>0.3196582367825028</v>
       </c>
       <c r="T82">
-        <v>4.024674834385698</v>
+        <v>4.236499825669156</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02274043082670811</v>
+        <v>0.02245968476711913</v>
       </c>
       <c r="W82">
-        <v>0.2304378064110622</v>
+        <v>0.2305040063319133</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2274043082670811</v>
+        <v>0.2245968476711913</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2474433101175253</v>
+        <v>0.2493433101175253</v>
       </c>
       <c r="C83">
-        <v>-316.9684231424496</v>
+        <v>-324.9495160848236</v>
       </c>
       <c r="D83">
-        <v>178.0155768575505</v>
+        <v>176.3984839151765</v>
       </c>
       <c r="E83">
-        <v>461.2840000000002</v>
+        <v>467.6480000000001</v>
       </c>
       <c r="F83">
-        <v>515.4840000000002</v>
+        <v>521.8480000000001</v>
       </c>
       <c r="G83">
         <v>20.5</v>
@@ -8093,37 +8093,37 @@
         <v>27.3</v>
       </c>
       <c r="M83">
-        <v>121.5511272</v>
+        <v>123.0517584</v>
       </c>
       <c r="N83">
-        <v>-94.25112720000004</v>
+        <v>-95.75175840000003</v>
       </c>
       <c r="O83">
-        <v>-9.425112720000005</v>
+        <v>-9.575175840000004</v>
       </c>
       <c r="P83">
-        <v>-84.82601448000004</v>
+        <v>-86.17658256000003</v>
       </c>
       <c r="Q83">
-        <v>-62.12601448000004</v>
+        <v>-63.47658256000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3196582367825028</v>
+        <v>0.3348725832704196</v>
       </c>
       <c r="T83">
-        <v>4.236499825669156</v>
+        <v>4.471860927095221</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02245968476711913</v>
+        <v>0.02218578617239816</v>
       </c>
       <c r="W83">
-        <v>0.2305040063319133</v>
+        <v>0.2305685916205485</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2245968476711913</v>
+        <v>0.2218578617239816</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2493433101175253</v>
+        <v>0.2512433101175253</v>
       </c>
       <c r="C84">
-        <v>-324.9495160848236</v>
+        <v>-332.9014941720081</v>
       </c>
       <c r="D84">
-        <v>176.3984839151765</v>
+        <v>174.810505827992</v>
       </c>
       <c r="E84">
-        <v>467.6480000000001</v>
+        <v>474.0120000000001</v>
       </c>
       <c r="F84">
-        <v>521.8480000000001</v>
+        <v>528.2120000000001</v>
       </c>
       <c r="G84">
         <v>20.5</v>
@@ -8175,37 +8175,37 @@
         <v>27.3</v>
       </c>
       <c r="M84">
-        <v>123.0517584</v>
+        <v>124.5523896</v>
       </c>
       <c r="N84">
-        <v>-95.75175840000003</v>
+        <v>-97.25238960000003</v>
       </c>
       <c r="O84">
-        <v>-9.575175840000004</v>
+        <v>-9.725238960000004</v>
       </c>
       <c r="P84">
-        <v>-86.17658256000003</v>
+        <v>-87.52715064000003</v>
       </c>
       <c r="Q84">
-        <v>-63.47658256000003</v>
+        <v>-64.82715064000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3348725832704196</v>
+        <v>0.3518768528745619</v>
       </c>
       <c r="T84">
-        <v>4.471860927095221</v>
+        <v>4.734911569865528</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02218578617239816</v>
+        <v>0.02191848754381505</v>
       </c>
       <c r="W84">
-        <v>0.2305685916205485</v>
+        <v>0.2306316206371684</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2218578617239816</v>
+        <v>0.2191848754381505</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2512433101175253</v>
+        <v>0.2531433101175253</v>
       </c>
       <c r="C85">
-        <v>-332.9014941720081</v>
+        <v>-340.8251366838122</v>
       </c>
       <c r="D85">
-        <v>174.810505827992</v>
+        <v>173.250863316188</v>
       </c>
       <c r="E85">
-        <v>474.0120000000001</v>
+        <v>480.3760000000001</v>
       </c>
       <c r="F85">
-        <v>528.2120000000001</v>
+        <v>534.5760000000001</v>
       </c>
       <c r="G85">
         <v>20.5</v>
@@ -8257,37 +8257,37 @@
         <v>27.3</v>
       </c>
       <c r="M85">
-        <v>124.5523896</v>
+        <v>126.0530208</v>
       </c>
       <c r="N85">
-        <v>-97.25238960000003</v>
+        <v>-98.75302080000004</v>
       </c>
       <c r="O85">
-        <v>-9.725238960000004</v>
+        <v>-9.875302080000004</v>
       </c>
       <c r="P85">
-        <v>-87.52715064000003</v>
+        <v>-88.87771872000005</v>
       </c>
       <c r="Q85">
-        <v>-64.82715064000003</v>
+        <v>-66.17771872000004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3518768528745619</v>
+        <v>0.3710066561792221</v>
       </c>
       <c r="T85">
-        <v>4.734911569865528</v>
+        <v>5.030843542982125</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02191848754381505</v>
+        <v>0.02165755316829344</v>
       </c>
       <c r="W85">
-        <v>0.2306316206371684</v>
+        <v>0.2306931489629164</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2191848754381505</v>
+        <v>0.2165755316829344</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2531433101175253</v>
+        <v>0.2550433101175253</v>
       </c>
       <c r="C86">
-        <v>-340.8251366838119</v>
+        <v>-348.7211953353367</v>
       </c>
       <c r="D86">
-        <v>173.2508633161881</v>
+        <v>171.7188046646634</v>
       </c>
       <c r="E86">
-        <v>480.376</v>
+        <v>486.7400000000001</v>
       </c>
       <c r="F86">
-        <v>534.576</v>
+        <v>540.9400000000001</v>
       </c>
       <c r="G86">
         <v>20.5</v>
@@ -8339,37 +8339,37 @@
         <v>27.3</v>
       </c>
       <c r="M86">
-        <v>126.0530208</v>
+        <v>127.553652</v>
       </c>
       <c r="N86">
-        <v>-98.75302080000002</v>
+        <v>-100.253652</v>
       </c>
       <c r="O86">
-        <v>-9.875302080000003</v>
+        <v>-10.0253652</v>
       </c>
       <c r="P86">
-        <v>-88.87771872000002</v>
+        <v>-90.22828680000001</v>
       </c>
       <c r="Q86">
-        <v>-66.17771872000002</v>
+        <v>-67.5282868</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3710066561792218</v>
+        <v>0.3926870999245033</v>
       </c>
       <c r="T86">
-        <v>5.030843542982121</v>
+        <v>5.366233112514263</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02165755316829345</v>
+        <v>0.02140275842513705</v>
       </c>
       <c r="W86">
-        <v>0.2306931489629164</v>
+        <v>0.2307532295633527</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2165755316829344</v>
+        <v>0.2140275842513705</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2550433101175253</v>
+        <v>0.2569433101175253</v>
       </c>
       <c r="C87">
-        <v>-348.7211953353367</v>
+        <v>-356.5903954850663</v>
       </c>
       <c r="D87">
-        <v>171.7188046646634</v>
+        <v>170.2136045149337</v>
       </c>
       <c r="E87">
-        <v>486.7400000000001</v>
+        <v>493.1040000000001</v>
       </c>
       <c r="F87">
-        <v>540.9400000000001</v>
+        <v>547.3040000000001</v>
       </c>
       <c r="G87">
         <v>20.5</v>
@@ -8421,37 +8421,37 @@
         <v>27.3</v>
       </c>
       <c r="M87">
-        <v>127.553652</v>
+        <v>129.0542832</v>
       </c>
       <c r="N87">
-        <v>-100.253652</v>
+        <v>-101.7542832</v>
       </c>
       <c r="O87">
-        <v>-10.0253652</v>
+        <v>-10.17542832</v>
       </c>
       <c r="P87">
-        <v>-90.22828680000001</v>
+        <v>-91.57885488000002</v>
       </c>
       <c r="Q87">
-        <v>-67.5282868</v>
+        <v>-68.87885488000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3926870999245033</v>
+        <v>0.4174647499191108</v>
       </c>
       <c r="T87">
-        <v>5.366233112514263</v>
+        <v>5.749535477693853</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02140275842513705</v>
+        <v>0.02115388914112383</v>
       </c>
       <c r="W87">
-        <v>0.2307532295633527</v>
+        <v>0.230811912940523</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2140275842513705</v>
+        <v>0.2115388914112383</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2569433101175253</v>
+        <v>0.2588433101175253</v>
       </c>
       <c r="C88">
-        <v>-356.5903954850663</v>
+        <v>-364.4334372799747</v>
       </c>
       <c r="D88">
-        <v>170.2136045149337</v>
+        <v>168.7345627200254</v>
       </c>
       <c r="E88">
-        <v>493.1040000000001</v>
+        <v>499.4680000000001</v>
       </c>
       <c r="F88">
-        <v>547.3040000000001</v>
+        <v>553.6680000000001</v>
       </c>
       <c r="G88">
         <v>20.5</v>
@@ -8503,37 +8503,37 @@
         <v>27.3</v>
       </c>
       <c r="M88">
-        <v>129.0542832</v>
+        <v>130.5549144</v>
       </c>
       <c r="N88">
-        <v>-101.7542832</v>
+        <v>-103.2549144</v>
       </c>
       <c r="O88">
-        <v>-10.17542832</v>
+        <v>-10.32549144</v>
       </c>
       <c r="P88">
-        <v>-91.57885488000002</v>
+        <v>-92.92942296000003</v>
       </c>
       <c r="Q88">
-        <v>-68.87885488000002</v>
+        <v>-70.22942296000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4174647499191108</v>
+        <v>0.4460543460667346</v>
       </c>
       <c r="T88">
-        <v>5.749535477693853</v>
+        <v>6.191807437516457</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02115388914112383</v>
+        <v>0.02091074099007643</v>
       </c>
       <c r="W88">
-        <v>0.230811912940523</v>
+        <v>0.23086924727454</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2115388914112383</v>
+        <v>0.2091074099007643</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2588433101175253</v>
+        <v>0.2607433101175253</v>
       </c>
       <c r="C89">
-        <v>-364.4334372799747</v>
+        <v>-372.2509967414447</v>
       </c>
       <c r="D89">
-        <v>168.7345627200254</v>
+        <v>167.2810032585554</v>
       </c>
       <c r="E89">
-        <v>499.4680000000001</v>
+        <v>505.8320000000001</v>
       </c>
       <c r="F89">
-        <v>553.6680000000001</v>
+        <v>560.032</v>
       </c>
       <c r="G89">
         <v>20.5</v>
@@ -8585,37 +8585,37 @@
         <v>27.3</v>
       </c>
       <c r="M89">
-        <v>130.5549144</v>
+        <v>132.0555456</v>
       </c>
       <c r="N89">
-        <v>-103.2549144</v>
+        <v>-104.7555456</v>
       </c>
       <c r="O89">
-        <v>-10.32549144</v>
+        <v>-10.47555456</v>
       </c>
       <c r="P89">
-        <v>-92.92942296000003</v>
+        <v>-94.27999104000001</v>
       </c>
       <c r="Q89">
-        <v>-70.22942296000002</v>
+        <v>-71.57999104000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4460543460667346</v>
+        <v>0.4794088749056292</v>
       </c>
       <c r="T89">
-        <v>6.191807437516457</v>
+        <v>6.707791390642829</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02091074099007643</v>
+        <v>0.02067311893337102</v>
       </c>
       <c r="W89">
-        <v>0.23086924727454</v>
+        <v>0.2309252785555111</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2091074099007643</v>
+        <v>0.2067311893337102</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2607433101175253</v>
+        <v>0.2626433101175253</v>
       </c>
       <c r="C90">
-        <v>-372.2509967414447</v>
+        <v>-380.0437267955396</v>
       </c>
       <c r="D90">
-        <v>167.2810032585554</v>
+        <v>165.8522732044605</v>
       </c>
       <c r="E90">
-        <v>505.8320000000001</v>
+        <v>512.196</v>
       </c>
       <c r="F90">
-        <v>560.032</v>
+        <v>566.3960000000001</v>
       </c>
       <c r="G90">
         <v>20.5</v>
@@ -8667,37 +8667,37 @@
         <v>27.3</v>
       </c>
       <c r="M90">
-        <v>132.0555456</v>
+        <v>133.5561768</v>
       </c>
       <c r="N90">
-        <v>-104.7555456</v>
+        <v>-106.2561768</v>
       </c>
       <c r="O90">
-        <v>-10.47555456</v>
+        <v>-10.62561768</v>
       </c>
       <c r="P90">
-        <v>-94.27999104000001</v>
+        <v>-95.63055912000003</v>
       </c>
       <c r="Q90">
-        <v>-71.57999104000001</v>
+        <v>-72.93055912000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4794088749056292</v>
+        <v>0.5188278635334137</v>
       </c>
       <c r="T90">
-        <v>6.707791390642829</v>
+        <v>7.317590607973997</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02067311893337102</v>
+        <v>0.0204408366981646</v>
       </c>
       <c r="W90">
-        <v>0.2309252785555111</v>
+        <v>0.2309800507065728</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2067311893337102</v>
+        <v>0.204408366981646</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2626433101175253</v>
+        <v>0.2645433101175253</v>
       </c>
       <c r="C91">
-        <v>-380.0437267955396</v>
+        <v>-387.8122582509243</v>
       </c>
       <c r="D91">
-        <v>165.8522732044605</v>
+        <v>164.4477417490758</v>
       </c>
       <c r="E91">
-        <v>512.196</v>
+        <v>518.5600000000001</v>
       </c>
       <c r="F91">
-        <v>566.3960000000001</v>
+        <v>572.7600000000001</v>
       </c>
       <c r="G91">
         <v>20.5</v>
@@ -8749,37 +8749,37 @@
         <v>27.3</v>
       </c>
       <c r="M91">
-        <v>133.5561768</v>
+        <v>135.056808</v>
       </c>
       <c r="N91">
-        <v>-106.2561768</v>
+        <v>-107.756808</v>
       </c>
       <c r="O91">
-        <v>-10.62561768</v>
+        <v>-10.7756808</v>
       </c>
       <c r="P91">
-        <v>-95.63055912000003</v>
+        <v>-96.98112720000002</v>
       </c>
       <c r="Q91">
-        <v>-72.93055912000003</v>
+        <v>-74.28112720000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5188278635334137</v>
+        <v>0.5661306498867551</v>
       </c>
       <c r="T91">
-        <v>7.317590607973997</v>
+        <v>8.049349668771397</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0204408366981646</v>
+        <v>0.02021371629040722</v>
       </c>
       <c r="W91">
-        <v>0.2309800507065728</v>
+        <v>0.231033605698722</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.204408366981646</v>
+        <v>0.2021371629040721</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2645433101175253</v>
+        <v>0.2664433101175253</v>
       </c>
       <c r="C92">
-        <v>-387.8122582509243</v>
+        <v>-395.5572007275146</v>
       </c>
       <c r="D92">
-        <v>164.4477417490758</v>
+        <v>163.0667992724856</v>
       </c>
       <c r="E92">
-        <v>518.5600000000001</v>
+        <v>524.9240000000001</v>
       </c>
       <c r="F92">
-        <v>572.7600000000001</v>
+        <v>579.1240000000001</v>
       </c>
       <c r="G92">
         <v>20.5</v>
@@ -8831,37 +8831,37 @@
         <v>27.3</v>
       </c>
       <c r="M92">
-        <v>135.056808</v>
+        <v>136.5574392</v>
       </c>
       <c r="N92">
-        <v>-107.756808</v>
+        <v>-109.2574392</v>
       </c>
       <c r="O92">
-        <v>-10.7756808</v>
+        <v>-10.92574392</v>
       </c>
       <c r="P92">
-        <v>-96.98112720000002</v>
+        <v>-98.33169528000003</v>
       </c>
       <c r="Q92">
-        <v>-74.28112720000001</v>
+        <v>-75.63169528000003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5661306498867551</v>
+        <v>0.6239451665408391</v>
       </c>
       <c r="T92">
-        <v>8.049349668771397</v>
+        <v>8.943721854190441</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02021371629040722</v>
+        <v>0.01999158753996318</v>
       </c>
       <c r="W92">
-        <v>0.231033605698722</v>
+        <v>0.2310859836580767</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2021371629040721</v>
+        <v>0.1999158753996317</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2664433101175253</v>
+        <v>0.2683433101175253</v>
       </c>
       <c r="C93">
-        <v>-395.5572007275146</v>
+        <v>-403.2791435387265</v>
       </c>
       <c r="D93">
-        <v>163.0667992724856</v>
+        <v>161.7088564612735</v>
       </c>
       <c r="E93">
-        <v>524.9240000000001</v>
+        <v>531.288</v>
       </c>
       <c r="F93">
-        <v>579.1240000000001</v>
+        <v>585.4880000000001</v>
       </c>
       <c r="G93">
         <v>20.5</v>
@@ -8913,37 +8913,37 @@
         <v>27.3</v>
       </c>
       <c r="M93">
-        <v>136.5574392</v>
+        <v>138.0580704</v>
       </c>
       <c r="N93">
-        <v>-109.2574392</v>
+        <v>-110.7580704</v>
       </c>
       <c r="O93">
-        <v>-10.92574392</v>
+        <v>-11.07580704</v>
       </c>
       <c r="P93">
-        <v>-98.33169528000003</v>
+        <v>-99.68226336000002</v>
       </c>
       <c r="Q93">
-        <v>-75.63169528000003</v>
+        <v>-76.98226336000002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6239451665408391</v>
+        <v>0.6962133123584442</v>
       </c>
       <c r="T93">
-        <v>8.943721854190441</v>
+        <v>10.06168708596425</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01999158753996318</v>
+        <v>0.01977428767539836</v>
       </c>
       <c r="W93">
-        <v>0.2310859836580767</v>
+        <v>0.2311372229661411</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1999158753996317</v>
+        <v>0.1977428767539836</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2683433101175253</v>
+        <v>0.2702433101175253</v>
       </c>
       <c r="C94">
-        <v>-403.2791435387265</v>
+        <v>-410.9786565300082</v>
       </c>
       <c r="D94">
-        <v>161.7088564612735</v>
+        <v>160.3733434699919</v>
       </c>
       <c r="E94">
-        <v>531.288</v>
+        <v>537.652</v>
       </c>
       <c r="F94">
-        <v>585.4880000000001</v>
+        <v>591.8520000000001</v>
       </c>
       <c r="G94">
         <v>20.5</v>
@@ -8995,37 +8995,37 @@
         <v>27.3</v>
       </c>
       <c r="M94">
-        <v>138.0580704</v>
+        <v>139.5587016</v>
       </c>
       <c r="N94">
-        <v>-110.7580704</v>
+        <v>-112.2587016</v>
       </c>
       <c r="O94">
-        <v>-11.07580704</v>
+        <v>-11.22587016</v>
       </c>
       <c r="P94">
-        <v>-99.68226336000002</v>
+        <v>-101.03283144</v>
       </c>
       <c r="Q94">
-        <v>-76.98226336000002</v>
+        <v>-78.33283144000004</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6962133123584442</v>
+        <v>0.789129499838222</v>
       </c>
       <c r="T94">
-        <v>10.06168708596425</v>
+        <v>11.49907095538772</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01977428767539836</v>
+        <v>0.01956166092620053</v>
       </c>
       <c r="W94">
-        <v>0.2311372229661411</v>
+        <v>0.2311873603536019</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1977428767539836</v>
+        <v>0.1956166092620053</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2702433101175253</v>
+        <v>0.2721433101175253</v>
       </c>
       <c r="C95">
-        <v>-410.9786565300082</v>
+        <v>-418.6562908761595</v>
       </c>
       <c r="D95">
-        <v>160.3733434699919</v>
+        <v>159.0597091238407</v>
       </c>
       <c r="E95">
-        <v>537.652</v>
+        <v>544.0160000000001</v>
       </c>
       <c r="F95">
-        <v>591.8520000000001</v>
+        <v>598.2160000000001</v>
       </c>
       <c r="G95">
         <v>20.5</v>
@@ -9077,37 +9077,37 @@
         <v>27.3</v>
       </c>
       <c r="M95">
-        <v>139.5587016</v>
+        <v>141.0593328</v>
       </c>
       <c r="N95">
-        <v>-112.2587016</v>
+        <v>-113.7593328</v>
       </c>
       <c r="O95">
-        <v>-11.22587016</v>
+        <v>-11.37593328</v>
       </c>
       <c r="P95">
-        <v>-101.03283144</v>
+        <v>-102.38339952</v>
       </c>
       <c r="Q95">
-        <v>-78.33283144000004</v>
+        <v>-79.68339952000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.789129499838222</v>
+        <v>0.9130177498112592</v>
       </c>
       <c r="T95">
-        <v>11.49907095538772</v>
+        <v>13.41558278128567</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01956166092620053</v>
+        <v>0.01935355815038989</v>
       </c>
       <c r="W95">
-        <v>0.2311873603536019</v>
+        <v>0.2312364309881381</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1956166092620053</v>
+        <v>0.1935355815038988</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2721433101175253</v>
+        <v>0.2740433101175253</v>
       </c>
       <c r="C96">
-        <v>-418.6562908761595</v>
+        <v>-426.3125798397858</v>
       </c>
       <c r="D96">
-        <v>159.0597091238407</v>
+        <v>157.7674201602143</v>
       </c>
       <c r="E96">
-        <v>544.0160000000001</v>
+        <v>550.3800000000001</v>
       </c>
       <c r="F96">
-        <v>598.2160000000001</v>
+        <v>604.5800000000002</v>
       </c>
       <c r="G96">
         <v>20.5</v>
@@ -9159,37 +9159,37 @@
         <v>27.3</v>
       </c>
       <c r="M96">
-        <v>141.0593328</v>
+        <v>142.559964</v>
       </c>
       <c r="N96">
-        <v>-113.7593328</v>
+        <v>-115.259964</v>
       </c>
       <c r="O96">
-        <v>-11.37593328</v>
+        <v>-11.5259964</v>
       </c>
       <c r="P96">
-        <v>-102.38339952</v>
+        <v>-103.7339676</v>
       </c>
       <c r="Q96">
-        <v>-79.68339952000002</v>
+        <v>-81.03396760000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9130177498112592</v>
+        <v>1.086461299773512</v>
       </c>
       <c r="T96">
-        <v>13.41558278128567</v>
+        <v>16.09869933754281</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01935355815038989</v>
+        <v>0.01914983648564894</v>
       </c>
       <c r="W96">
-        <v>0.2312364309881381</v>
+        <v>0.231284468556684</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1935355815038988</v>
+        <v>0.1914983648564894</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2740433101175253</v>
+        <v>0.2759433101175253</v>
       </c>
       <c r="C97">
-        <v>-426.3125798397858</v>
+        <v>-433.9480394930771</v>
       </c>
       <c r="D97">
-        <v>157.7674201602143</v>
+        <v>156.4959605069231</v>
       </c>
       <c r="E97">
-        <v>550.3800000000001</v>
+        <v>556.7440000000001</v>
       </c>
       <c r="F97">
-        <v>604.5800000000002</v>
+        <v>610.9440000000002</v>
       </c>
       <c r="G97">
         <v>20.5</v>
@@ -9241,37 +9241,37 @@
         <v>27.3</v>
       </c>
       <c r="M97">
-        <v>142.559964</v>
+        <v>144.0605952000001</v>
       </c>
       <c r="N97">
-        <v>-115.259964</v>
+        <v>-116.7605952000001</v>
       </c>
       <c r="O97">
-        <v>-11.5259964</v>
+        <v>-11.67605952000001</v>
       </c>
       <c r="P97">
-        <v>-103.7339676</v>
+        <v>-105.08453568</v>
       </c>
       <c r="Q97">
-        <v>-81.03396760000003</v>
+        <v>-82.38453568000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.086461299773512</v>
+        <v>1.34662662471689</v>
       </c>
       <c r="T97">
-        <v>16.09869933754281</v>
+        <v>20.12337417192852</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01914983648564894</v>
+        <v>0.01895035902225676</v>
       </c>
       <c r="W97">
-        <v>0.231284468556684</v>
+        <v>0.2313315053425519</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1914983648564894</v>
+        <v>0.1895035902225676</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2759433101175253</v>
+        <v>0.2778433101175253</v>
       </c>
       <c r="C98">
-        <v>-433.948039493077</v>
+        <v>-441.5631694049636</v>
       </c>
       <c r="D98">
-        <v>156.4959605069231</v>
+        <v>155.2448305950365</v>
       </c>
       <c r="E98">
-        <v>556.744</v>
+        <v>563.1080000000001</v>
       </c>
       <c r="F98">
-        <v>610.9440000000001</v>
+        <v>617.3080000000001</v>
       </c>
       <c r="G98">
         <v>20.5</v>
@@ -9323,37 +9323,37 @@
         <v>27.3</v>
       </c>
       <c r="M98">
-        <v>144.0605952</v>
+        <v>145.5612264</v>
       </c>
       <c r="N98">
-        <v>-116.7605952</v>
+        <v>-118.2612264</v>
       </c>
       <c r="O98">
-        <v>-11.67605952</v>
+        <v>-11.82612264</v>
       </c>
       <c r="P98">
-        <v>-105.08453568</v>
+        <v>-106.43510376</v>
       </c>
       <c r="Q98">
-        <v>-82.38453568000001</v>
+        <v>-83.73510376000003</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.346626624716887</v>
+        <v>1.780235499622515</v>
       </c>
       <c r="T98">
-        <v>20.12337417192847</v>
+        <v>26.83116556257129</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01895035902225677</v>
+        <v>0.01875499449625412</v>
       </c>
       <c r="W98">
-        <v>0.2313315053425519</v>
+        <v>0.2313775722977833</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1895035902225676</v>
+        <v>0.1875499449625412</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2778433101175253</v>
+        <v>0.2797433101175253</v>
       </c>
       <c r="C99">
-        <v>-441.5631694049636</v>
+        <v>-449.1584532955731</v>
       </c>
       <c r="D99">
-        <v>155.2448305950365</v>
+        <v>154.013546704427</v>
       </c>
       <c r="E99">
-        <v>563.1080000000001</v>
+        <v>569.472</v>
       </c>
       <c r="F99">
-        <v>617.3080000000001</v>
+        <v>623.672</v>
       </c>
       <c r="G99">
         <v>20.5</v>
@@ -9405,37 +9405,37 @@
         <v>27.3</v>
       </c>
       <c r="M99">
-        <v>145.5612264</v>
+        <v>147.0618576</v>
       </c>
       <c r="N99">
-        <v>-118.2612264</v>
+        <v>-119.7618576</v>
       </c>
       <c r="O99">
-        <v>-11.82612264</v>
+        <v>-11.97618576</v>
       </c>
       <c r="P99">
-        <v>-106.43510376</v>
+        <v>-107.78567184</v>
       </c>
       <c r="Q99">
-        <v>-83.73510376000003</v>
+        <v>-85.08567184000002</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.780235499622515</v>
+        <v>2.647453249433773</v>
       </c>
       <c r="T99">
-        <v>26.83116556257129</v>
+        <v>40.24674834385694</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01875499449625412</v>
+        <v>0.01856361700139438</v>
       </c>
       <c r="W99">
-        <v>0.2313775722977833</v>
+        <v>0.2314226991110712</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1875499449625412</v>
+        <v>0.1856361700139438</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2797433101175253</v>
+        <v>0.2816433101175253</v>
       </c>
       <c r="C100">
-        <v>-449.1584532955731</v>
+        <v>-456.7343596597882</v>
       </c>
       <c r="D100">
-        <v>154.013546704427</v>
+        <v>152.8016403402119</v>
       </c>
       <c r="E100">
-        <v>569.472</v>
+        <v>575.836</v>
       </c>
       <c r="F100">
-        <v>623.672</v>
+        <v>630.0360000000001</v>
       </c>
       <c r="G100">
         <v>20.5</v>
@@ -9487,37 +9487,37 @@
         <v>27.3</v>
       </c>
       <c r="M100">
-        <v>147.0618576</v>
+        <v>148.5624888</v>
       </c>
       <c r="N100">
-        <v>-119.7618576</v>
+        <v>-121.2624888</v>
       </c>
       <c r="O100">
-        <v>-11.97618576</v>
+        <v>-12.12624888</v>
       </c>
       <c r="P100">
-        <v>-107.78567184</v>
+        <v>-109.13623992</v>
       </c>
       <c r="Q100">
-        <v>-85.08567184000002</v>
+        <v>-86.43623992000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.647453249433773</v>
+        <v>5.249106498867546</v>
       </c>
       <c r="T100">
-        <v>40.24674834385694</v>
+        <v>80.49349668771387</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01856361700139438</v>
+        <v>0.01837610571855202</v>
       </c>
       <c r="W100">
-        <v>0.2314226991110712</v>
+        <v>0.2314669142715655</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1856361700139438</v>
+        <v>0.1837610571855202</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2816433101175253</v>
-      </c>
-      <c r="C101">
-        <v>-456.7343596597882</v>
-      </c>
-      <c r="D101">
-        <v>152.8016403402119</v>
-      </c>
-      <c r="E101">
-        <v>575.836</v>
-      </c>
-      <c r="F101">
-        <v>630.0360000000001</v>
-      </c>
-      <c r="G101">
-        <v>20.5</v>
-      </c>
-      <c r="H101">
-        <v>582.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>50</v>
-      </c>
-      <c r="K101">
-        <v>22.7</v>
-      </c>
-      <c r="L101">
-        <v>27.3</v>
-      </c>
-      <c r="M101">
-        <v>148.5624888</v>
-      </c>
-      <c r="N101">
-        <v>-121.2624888</v>
-      </c>
-      <c r="O101">
-        <v>-12.12624888</v>
-      </c>
-      <c r="P101">
-        <v>-109.13623992</v>
-      </c>
-      <c r="Q101">
-        <v>-86.43623992000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.249106498867546</v>
-      </c>
-      <c r="T101">
-        <v>80.49349668771387</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01837610571855202</v>
-      </c>
-      <c r="W101">
-        <v>0.2314669142715655</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1837610571855202</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
